--- a/NorthernTrust/NT-KostenBepaling.xlsx
+++ b/NorthernTrust/NT-KostenBepaling.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7c741cee80ec8cf3/Financieel/IndexFondsenOnderzoek/KeuzeWelkIndexFonds/OnderzoekPerFonds/NorthernTrust/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="674" documentId="13_ncr:1_{0BEEB54A-A1B5-4808-9253-8C962E6DCC11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86629BA9-EB7D-441A-9D43-6924F1975B4B}"/>
+  <xr:revisionPtr revIDLastSave="750" documentId="13_ncr:1_{0BEEB54A-A1B5-4808-9253-8C962E6DCC11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3B76FBF-B5DA-43D1-BE16-84A1CFEFB23C}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aannames" sheetId="4" r:id="rId1"/>
@@ -296,7 +296,7 @@
     <author>Gerben</author>
   </authors>
   <commentList>
-    <comment ref="N2" authorId="0" shapeId="0" xr:uid="{434CD842-3C43-4334-B2E1-FAF0941512B8}">
+    <comment ref="O2" authorId="0" shapeId="0" xr:uid="{434CD842-3C43-4334-B2E1-FAF0941512B8}">
       <text>
         <r>
           <rPr>
@@ -320,7 +320,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O2" authorId="0" shapeId="0" xr:uid="{EE1FF351-82F3-401D-BF5F-E210234F658F}">
+    <comment ref="P2" authorId="0" shapeId="0" xr:uid="{EE1FF351-82F3-401D-BF5F-E210234F658F}">
       <text>
         <r>
           <rPr>
@@ -425,7 +425,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="127">
   <si>
     <t>Transaction costs and interest expenses are excluded from the calculation.</t>
   </si>
@@ -790,6 +790,24 @@
   </si>
   <si>
     <t>gek, een gat?</t>
+  </si>
+  <si>
+    <t>Fund return</t>
+  </si>
+  <si>
+    <t>Gross index return</t>
+  </si>
+  <si>
+    <t>Gross tracking diff</t>
+  </si>
+  <si>
+    <t>Fund turnover</t>
+  </si>
+  <si>
+    <t>TER</t>
+  </si>
+  <si>
+    <t>Onverklaarbaar verschil</t>
   </si>
 </sst>
 </file>
@@ -980,6 +998,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1364,18 +1386,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:L42"/>
+  <dimension ref="B2:O42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="36.42578125" customWidth="1"/>
-    <col min="3" max="8" width="17.7109375" customWidth="1"/>
-    <col min="9" max="9" width="6.140625" customWidth="1"/>
-    <col min="10" max="10" width="13.28515625" customWidth="1"/>
-    <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="122.140625" customWidth="1"/>
+    <col min="3" max="11" width="17.7109375" customWidth="1"/>
+    <col min="12" max="12" width="6.140625" customWidth="1"/>
+    <col min="13" max="13" width="13.28515625" customWidth="1"/>
+    <col min="14" max="14" width="18" customWidth="1"/>
+    <col min="15" max="15" width="122.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B2" s="10" t="s">
         <v>3</v>
       </c>
@@ -1387,19 +1409,22 @@
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
-      <c r="L2" s="1" t="s">
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="O2" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>21</v>
       </c>
-      <c r="L3" t="s">
+      <c r="O3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C4" s="1">
         <v>2016</v>
       </c>
@@ -1418,15 +1443,24 @@
       <c r="H4" s="1">
         <v>2021</v>
       </c>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1" t="s">
+      <c r="I4" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J4" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K4" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L4" t="s">
+      <c r="O4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>1</v>
       </c>
@@ -1448,12 +1482,15 @@
       <c r="H5" s="11">
         <v>526476</v>
       </c>
-      <c r="I5" s="2"/>
-      <c r="L5" t="s">
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="2"/>
+      <c r="O5" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>7</v>
       </c>
@@ -1475,9 +1512,12 @@
       <c r="H6" s="11">
         <v>4671196104</v>
       </c>
-      <c r="I6" s="2"/>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="2"/>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>15</v>
       </c>
@@ -1506,13 +1546,16 @@
         <v>1.1270689311227427E-4</v>
       </c>
       <c r="I7" s="4"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="3"/>
-      <c r="L7" t="s">
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="3"/>
+      <c r="O7" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>16</v>
       </c>
@@ -1541,9 +1584,12 @@
         <v>1.7136259660773064E-5</v>
       </c>
       <c r="I8" s="4"/>
-      <c r="J8" s="5"/>
-    </row>
-    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="5"/>
+    </row>
+    <row r="9" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>26</v>
       </c>
@@ -1572,15 +1618,18 @@
         <v>1.2984315277304734E-4</v>
       </c>
       <c r="I9" s="4"/>
-      <c r="J9" s="5">
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="5">
         <f>AVERAGE(C9:H9)</f>
         <v>1.434146530285744E-4</v>
       </c>
-      <c r="L9" t="s">
+      <c r="O9" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>71</v>
       </c>
@@ -1602,26 +1651,38 @@
       <c r="H10" s="3">
         <v>1.5E-3</v>
       </c>
-      <c r="I10" s="4"/>
-      <c r="J10" s="6">
+      <c r="I10" s="3">
+        <v>1.5E-3</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1.5E-3</v>
+      </c>
+      <c r="K10" s="3">
+        <v>1.5E-3</v>
+      </c>
+      <c r="L10" s="4"/>
+      <c r="M10" s="6">
         <f>AVERAGE(C10:H10)</f>
         <v>1.0499999999999999E-3</v>
       </c>
-      <c r="L10" t="s">
+      <c r="O10" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="6"/>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="6"/>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>67</v>
       </c>
@@ -1648,13 +1709,16 @@
         <f>4740622-H5</f>
         <v>4214146</v>
       </c>
-      <c r="I12" s="4"/>
-      <c r="J12" s="6"/>
-      <c r="L12" t="s">
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="6"/>
+      <c r="O12" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>105</v>
       </c>
@@ -1682,16 +1746,19 @@
         <f t="shared" si="2"/>
         <v>9.0215565910225376E-4</v>
       </c>
-      <c r="I13" s="4"/>
-      <c r="J13" s="6">
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="6">
         <f>AVERAGE(C13:H13)</f>
         <v>8.2359797066475053E-4</v>
       </c>
-      <c r="L13" t="s">
+      <c r="O13" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>102</v>
       </c>
@@ -1716,13 +1783,16 @@
         <f t="shared" si="3"/>
         <v>4740622</v>
       </c>
-      <c r="I14" s="4"/>
-      <c r="J14" s="6"/>
-      <c r="L14" t="s">
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="6"/>
+      <c r="O14" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>104</v>
       </c>
@@ -1747,23 +1817,29 @@
         <f t="shared" si="4"/>
         <v>1.0148625522145281E-3</v>
       </c>
-      <c r="I15" s="4"/>
-      <c r="J15" s="6"/>
-    </row>
-    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="6"/>
+    </row>
+    <row r="16" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="6"/>
-      <c r="L16" t="s">
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="6"/>
+      <c r="O16" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="17" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>91</v>
       </c>
@@ -1789,14 +1865,21 @@
       <c r="H17" s="24">
         <v>0.08</v>
       </c>
-      <c r="I17" s="4"/>
-      <c r="J17" s="37">
+      <c r="I17" s="24">
+        <v>0.02</v>
+      </c>
+      <c r="J17" s="24">
+        <v>0.01</v>
+      </c>
+      <c r="K17" s="24"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="37">
         <f>AVERAGE(E17:H17)</f>
         <v>0.155</v>
       </c>
-      <c r="K17" s="4"/>
-    </row>
-    <row r="18" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N17" s="4"/>
+    </row>
+    <row r="18" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>96</v>
       </c>
@@ -1818,22 +1901,28 @@
       <c r="H18" s="24">
         <v>7.9200000000000007E-2</v>
       </c>
-      <c r="I18" s="4"/>
-      <c r="J18" s="37">
+      <c r="I18" s="24"/>
+      <c r="J18" s="24"/>
+      <c r="K18" s="24"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="37">
         <f>AVERAGE(E18:H18)</f>
         <v>7.6575000000000004E-2</v>
       </c>
     </row>
-    <row r="19" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
-      <c r="J19" s="5"/>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="5"/>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>110</v>
       </c>
@@ -1848,13 +1937,16 @@
       <c r="H20" s="3">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="I20" s="4"/>
-      <c r="J20" s="5">
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="5">
         <f>AVERAGE(F20:H20)</f>
         <v>2.9999999999999997E-4</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C21" s="3"/>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
@@ -1862,14 +1954,17 @@
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
-      <c r="J21" s="5"/>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="5"/>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>82</v>
       </c>
       <c r="C22" s="6">
-        <f>J9+J13</f>
+        <f>M9+M13</f>
         <v>9.6701262369332491E-4</v>
       </c>
       <c r="D22" t="s">
@@ -1880,15 +1975,18 @@
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
-      <c r="J22" s="5"/>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="5"/>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>114</v>
       </c>
       <c r="C23" s="6">
-        <f>('Tracking Difference'!N7/100)-C22</f>
-        <v>1.3329873763066728E-3</v>
+        <f>('Tracking Difference'!O7/100)-C22</f>
+        <v>1.5552095985288945E-3</v>
       </c>
       <c r="D23" t="s">
         <v>120</v>
@@ -1898,23 +1996,29 @@
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
-      <c r="J23" s="5"/>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
+      <c r="M23" s="5"/>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C24" s="6"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
-      <c r="J24" s="5"/>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="5"/>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>82</v>
       </c>
       <c r="C25" s="6">
-        <f>J9+J13+J20</f>
+        <f>M9+M13+M20</f>
         <v>1.2670126236933249E-3</v>
       </c>
       <c r="D25" t="s">
@@ -1925,15 +2029,18 @@
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
-      <c r="J25" s="5"/>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="5"/>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>114</v>
       </c>
       <c r="C26" s="6">
-        <f>('Tracking Difference'!N7/100)-C25</f>
-        <v>1.0329873763066729E-3</v>
+        <f>('Tracking Difference'!O7/100)-C25</f>
+        <v>1.2552095985288946E-3</v>
       </c>
       <c r="D26" t="s">
         <v>120</v>
@@ -1943,35 +2050,47 @@
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
-      <c r="J26" s="5"/>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+      <c r="M26" s="5"/>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C27" s="6"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
-      <c r="J27" s="5"/>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="5"/>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
-      <c r="J28" s="5"/>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+      <c r="M28" s="5"/>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C29" s="6"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
-      <c r="J29" s="5"/>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="5"/>
+    </row>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C30" s="3" t="s">
         <v>107</v>
       </c>
@@ -1983,10 +2102,13 @@
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
-      <c r="J30" s="5"/>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="5"/>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
         <v>113</v>
       </c>
@@ -1998,84 +2120,108 @@
         <f>C31+H20</f>
         <v>1.9298431527730473E-3</v>
       </c>
-      <c r="I31" s="4"/>
-      <c r="J31" s="5"/>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="L31" s="4"/>
+      <c r="M31" s="5"/>
+    </row>
+    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
-      <c r="J32" s="5"/>
-    </row>
-    <row r="33" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="J32" s="4"/>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="5"/>
+    </row>
+    <row r="33" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
-      <c r="J33" s="5"/>
-    </row>
-    <row r="34" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="5"/>
+    </row>
+    <row r="34" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C34" s="6"/>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
       <c r="I34" s="4"/>
-      <c r="J34" s="5"/>
-    </row>
-    <row r="35" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="5"/>
+    </row>
+    <row r="35" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C35" s="6"/>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
-      <c r="J35" s="5"/>
-      <c r="K35" s="5"/>
-    </row>
-    <row r="36" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+    </row>
+    <row r="36" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C36" s="32"/>
       <c r="D36" s="32"/>
       <c r="E36" s="32"/>
       <c r="F36" s="32"/>
       <c r="G36" s="32"/>
       <c r="H36" s="32"/>
-    </row>
-    <row r="37" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="I36" s="32"/>
+      <c r="J36" s="32"/>
+      <c r="K36" s="32"/>
+    </row>
+    <row r="37" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C37" s="6"/>
       <c r="E37" s="32"/>
       <c r="F37" s="32"/>
       <c r="G37" s="32"/>
       <c r="H37" s="32"/>
-    </row>
-    <row r="38" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="I37" s="32"/>
+      <c r="J37" s="32"/>
+      <c r="K37" s="32"/>
+    </row>
+    <row r="38" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="32"/>
       <c r="F38" s="32"/>
       <c r="G38" s="32"/>
       <c r="H38" s="32"/>
-    </row>
-    <row r="39" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="I38" s="32"/>
+      <c r="J38" s="32"/>
+      <c r="K38" s="32"/>
+    </row>
+    <row r="39" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C39" s="39"/>
       <c r="D39" s="39"/>
       <c r="E39" s="32"/>
       <c r="F39" s="32"/>
       <c r="G39" s="32"/>
       <c r="H39" s="32"/>
-    </row>
-    <row r="40" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="I39" s="32"/>
+      <c r="J39" s="32"/>
+      <c r="K39" s="32"/>
+    </row>
+    <row r="40" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C41" s="6"/>
       <c r="D41" s="3"/>
     </row>
-    <row r="42" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C42" s="24"/>
       <c r="D42" s="6"/>
     </row>
@@ -2482,7 +2628,7 @@
         <v>114</v>
       </c>
       <c r="C20" s="6">
-        <f>('Tracking Difference'!N14/100)-C17</f>
+        <f>('Tracking Difference'!O14/100)-C17</f>
         <v>7.0382747195337761E-4</v>
       </c>
     </row>
@@ -2863,7 +3009,7 @@
         <v>114</v>
       </c>
       <c r="C24" s="6">
-        <f>('Tracking Difference'!N30/100)-C19</f>
+        <f>('Tracking Difference'!O30/100)-C19</f>
         <v>-1.3648925792929085E-3</v>
       </c>
     </row>
@@ -3183,7 +3329,7 @@
         <v>83</v>
       </c>
       <c r="C18" s="3">
-        <f>'Tracking Difference'!N22/100</f>
+        <f>'Tracking Difference'!O22/100</f>
         <v>3.274999999999998E-3</v>
       </c>
       <c r="D18" s="4" t="s">
@@ -3608,7 +3754,7 @@
         <v>83</v>
       </c>
       <c r="C18" s="3">
-        <f>'Tracking Difference'!N30/100</f>
+        <f>'Tracking Difference'!O30/100</f>
         <v>1.6499999999999959E-3</v>
       </c>
       <c r="D18" s="4" t="s">
@@ -4657,13 +4803,14 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F528616F-4365-4E03-AA99-F5C2282C78C2}">
-  <dimension ref="B2:R63"/>
+  <dimension ref="B2:AJ63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="73" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="22.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B2" s="16"/>
       <c r="C2" s="17">
         <v>2014</v>
@@ -4695,18 +4842,21 @@
       <c r="L2" s="17">
         <v>2023</v>
       </c>
-      <c r="M2" s="16"/>
-      <c r="N2" s="18" t="s">
+      <c r="M2" s="17">
+        <v>2024</v>
+      </c>
+      <c r="N2" s="16"/>
+      <c r="O2" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="O2" s="18" t="s">
+      <c r="P2" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B3" s="18" t="s">
         <v>61</v>
       </c>
@@ -4736,14 +4886,17 @@
       <c r="L3" s="19">
         <v>20.51</v>
       </c>
-      <c r="M3" s="16"/>
+      <c r="M3" s="19">
+        <v>26.97</v>
+      </c>
       <c r="N3" s="16"/>
-      <c r="O3" s="19"/>
-      <c r="R3" s="8" t="s">
+      <c r="O3" s="16"/>
+      <c r="P3" s="19"/>
+      <c r="S3" s="8" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="4" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B4" s="18" t="s">
         <v>43</v>
       </c>
@@ -4777,14 +4930,17 @@
       <c r="L4" s="19">
         <v>20.86</v>
       </c>
-      <c r="M4" s="16"/>
+      <c r="M4" s="19">
+        <v>27.4</v>
+      </c>
       <c r="N4" s="16"/>
       <c r="O4" s="16"/>
-      <c r="R4" s="8" t="s">
+      <c r="P4" s="16"/>
+      <c r="S4" s="8" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B5" s="18" t="s">
         <v>44</v>
       </c>
@@ -4814,18 +4970,21 @@
       <c r="L5" s="19">
         <v>20.260000000000002</v>
       </c>
-      <c r="M5" s="16"/>
+      <c r="M5" s="19">
+        <v>26.85</v>
+      </c>
       <c r="N5" s="16"/>
-      <c r="O5" s="19"/>
-    </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="O5" s="16"/>
+      <c r="P5" s="19"/>
+    </row>
+    <row r="6" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B6" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C6" s="19"/>
       <c r="D6" s="19"/>
       <c r="E6" s="19">
-        <f t="shared" ref="E6:L6" si="0">E3-E5</f>
+        <f t="shared" ref="E6:M6" si="0">E3-E5</f>
         <v>0.48000000000000043</v>
       </c>
       <c r="F6" s="19">
@@ -4856,21 +5015,25 @@
         <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
-      <c r="M6" s="16"/>
+      <c r="M6" s="19">
+        <f t="shared" si="0"/>
+        <v>0.11999999999999744</v>
+      </c>
       <c r="N6" s="16"/>
-      <c r="O6" s="19">
+      <c r="O6" s="16"/>
+      <c r="P6" s="19">
         <f>AVERAGE(E6:L6)</f>
         <v>0.34999999999999937</v>
       </c>
     </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B7" s="18" t="s">
         <v>45</v>
       </c>
       <c r="C7" s="19"/>
       <c r="D7" s="19"/>
       <c r="E7" s="19">
-        <f t="shared" ref="E7:L7" si="1">E4-E3</f>
+        <f t="shared" ref="E7:M7" si="1">E4-E3</f>
         <v>0.16999999999999993</v>
       </c>
       <c r="F7" s="19">
@@ -4901,14 +5064,18 @@
         <f t="shared" si="1"/>
         <v>0.34999999999999787</v>
       </c>
-      <c r="M7" s="16"/>
-      <c r="N7" s="29">
-        <f>AVERAGE(E7:L7)</f>
-        <v>0.22999999999999976</v>
-      </c>
-      <c r="O7" s="19"/>
-    </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="M7" s="19">
+        <f t="shared" si="1"/>
+        <v>0.42999999999999972</v>
+      </c>
+      <c r="N7" s="16"/>
+      <c r="O7" s="29">
+        <f>AVERAGE(E7:M7)</f>
+        <v>0.25222222222222196</v>
+      </c>
+      <c r="P7" s="19"/>
+    </row>
+    <row r="10" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B10" s="21" t="s">
         <v>60</v>
       </c>
@@ -4935,10 +5102,11 @@
       <c r="K10" s="22"/>
       <c r="L10" s="22"/>
       <c r="M10" s="22"/>
-      <c r="N10" s="20"/>
-      <c r="O10" s="22"/>
-    </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="N10" s="22"/>
+      <c r="O10" s="20"/>
+      <c r="P10" s="22"/>
+    </row>
+    <row r="11" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B11" s="21" t="s">
         <v>43</v>
       </c>
@@ -4969,10 +5137,11 @@
       <c r="K11" s="22"/>
       <c r="L11" s="22"/>
       <c r="M11" s="22"/>
-      <c r="N11" s="20"/>
-      <c r="O11" s="22"/>
-    </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="N11" s="22"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="22"/>
+    </row>
+    <row r="12" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B12" s="21" t="s">
         <v>44</v>
       </c>
@@ -4999,10 +5168,11 @@
       <c r="K12" s="22"/>
       <c r="L12" s="22"/>
       <c r="M12" s="22"/>
-      <c r="N12" s="20"/>
-      <c r="O12" s="22"/>
-    </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="N12" s="22"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="22"/>
+    </row>
+    <row r="13" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B13" s="21" t="s">
         <v>46</v>
       </c>
@@ -5036,51 +5206,169 @@
       <c r="L13" s="22"/>
       <c r="M13" s="22"/>
       <c r="N13" s="22"/>
-      <c r="O13" s="22">
+      <c r="O13" s="22"/>
+      <c r="P13" s="22">
         <f>AVERAGE(E13:J13)</f>
         <v>2.4999999999999689E-2</v>
       </c>
-    </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="AB13" s="1">
+        <f t="shared" ref="AB13:AD13" si="3">E2</f>
+        <v>2016</v>
+      </c>
+      <c r="AC13" s="1">
+        <f t="shared" si="3"/>
+        <v>2017</v>
+      </c>
+      <c r="AD13" s="1">
+        <f t="shared" si="3"/>
+        <v>2018</v>
+      </c>
+      <c r="AE13" s="1">
+        <f t="shared" ref="AE13:AJ15" si="4">H2</f>
+        <v>2019</v>
+      </c>
+      <c r="AF13" s="1">
+        <f t="shared" si="4"/>
+        <v>2020</v>
+      </c>
+      <c r="AG13" s="1">
+        <f t="shared" si="4"/>
+        <v>2021</v>
+      </c>
+      <c r="AH13" s="1">
+        <f t="shared" si="4"/>
+        <v>2022</v>
+      </c>
+      <c r="AI13" s="1">
+        <f t="shared" si="4"/>
+        <v>2023</v>
+      </c>
+      <c r="AJ13" s="1">
+        <f t="shared" si="4"/>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="14" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B14" s="21" t="s">
         <v>45</v>
       </c>
       <c r="C14" s="22"/>
       <c r="D14" s="22"/>
       <c r="E14" s="22">
-        <f t="shared" ref="E14:J14" si="3">E11-E10</f>
+        <f t="shared" ref="E14:J14" si="5">E11-E10</f>
         <v>0.63000000000000078</v>
       </c>
       <c r="F14" s="22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>8.0000000000001847E-2</v>
       </c>
       <c r="G14" s="22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.5</v>
       </c>
       <c r="H14" s="22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.25999999999999801</v>
       </c>
       <c r="I14" s="22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.46000000000000085</v>
       </c>
       <c r="J14" s="22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.26000000000000023</v>
       </c>
       <c r="K14" s="22"/>
       <c r="L14" s="22"/>
       <c r="M14" s="22"/>
-      <c r="N14" s="27">
+      <c r="N14" s="22"/>
+      <c r="O14" s="27">
         <f>AVERAGE(E14:J14)</f>
         <v>0.36500000000000027</v>
       </c>
-      <c r="O14" s="22"/>
-    </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P14" s="22"/>
+      <c r="AA14" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB14" s="26">
+        <f t="shared" ref="AB14:AD14" si="6">E3</f>
+        <v>10.55</v>
+      </c>
+      <c r="AC14" s="26">
+        <f t="shared" si="6"/>
+        <v>8.32</v>
+      </c>
+      <c r="AD14" s="26">
+        <f t="shared" si="6"/>
+        <v>-3.3</v>
+      </c>
+      <c r="AE14" s="26">
+        <f t="shared" si="4"/>
+        <v>30.93</v>
+      </c>
+      <c r="AF14" s="26">
+        <f t="shared" si="4"/>
+        <v>8.2200000000000006</v>
+      </c>
+      <c r="AG14" s="26">
+        <f t="shared" si="4"/>
+        <v>31.74</v>
+      </c>
+      <c r="AH14" s="26">
+        <f t="shared" si="4"/>
+        <v>-13.71</v>
+      </c>
+      <c r="AI14" s="26">
+        <f t="shared" si="4"/>
+        <v>20.51</v>
+      </c>
+      <c r="AJ14" s="26">
+        <f t="shared" si="4"/>
+        <v>26.97</v>
+      </c>
+    </row>
+    <row r="16" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="AA16" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB16" s="26">
+        <f>AB20-AB14</f>
+        <v>0.16999999999999993</v>
+      </c>
+      <c r="AC16" s="26">
+        <f>AC20-AC14</f>
+        <v>0.21999999999999886</v>
+      </c>
+      <c r="AD16" s="26">
+        <f>AD20-AD14</f>
+        <v>0.17999999999999972</v>
+      </c>
+      <c r="AE16" s="26">
+        <f>AE20-AE14</f>
+        <v>0.24000000000000199</v>
+      </c>
+      <c r="AF16" s="26">
+        <f>AF20-AF14</f>
+        <v>0.30999999999999872</v>
+      </c>
+      <c r="AG16" s="26">
+        <f>AG20-AG14</f>
+        <v>0.25</v>
+      </c>
+      <c r="AH16" s="26">
+        <f>AH20-AH14</f>
+        <v>0.12000000000000099</v>
+      </c>
+      <c r="AI16" s="26">
+        <f>AI20-AI14</f>
+        <v>0.34999999999999787</v>
+      </c>
+      <c r="AJ16" s="26">
+        <f>AJ20-AJ14</f>
+        <v>0.42999999999999972</v>
+      </c>
+    </row>
+    <row r="17" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B17" s="21" t="s">
         <v>59</v>
       </c>
@@ -5096,8 +5384,38 @@
       <c r="H17">
         <v>34.049999999999997</v>
       </c>
-    </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="AA17" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB17">
+        <v>0.03</v>
+      </c>
+      <c r="AC17">
+        <v>0.03</v>
+      </c>
+      <c r="AD17">
+        <v>0.12</v>
+      </c>
+      <c r="AE17">
+        <v>0.15</v>
+      </c>
+      <c r="AF17">
+        <v>0.15</v>
+      </c>
+      <c r="AG17">
+        <v>0.15</v>
+      </c>
+      <c r="AH17">
+        <v>0.15</v>
+      </c>
+      <c r="AI17">
+        <v>0.15</v>
+      </c>
+      <c r="AJ17">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="18" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B18" s="21" t="s">
         <v>56</v>
       </c>
@@ -5114,7 +5432,7 @@
         <v>33.590000000000003</v>
       </c>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B19" s="21" t="s">
         <v>57</v>
       </c>
@@ -5130,8 +5448,47 @@
       <c r="H19">
         <v>34.369999999999997</v>
       </c>
-    </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="AA19" t="s">
+        <v>124</v>
+      </c>
+      <c r="AB19" s="37">
+        <f>World!C17</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AC19" s="37">
+        <f>World!D17</f>
+        <v>0.01</v>
+      </c>
+      <c r="AD19" s="37">
+        <f>World!E17</f>
+        <v>0.09</v>
+      </c>
+      <c r="AE19" s="37">
+        <f>World!F17</f>
+        <v>0.26</v>
+      </c>
+      <c r="AF19" s="37">
+        <f>World!G17</f>
+        <v>0.19</v>
+      </c>
+      <c r="AG19" s="37">
+        <f>World!H17</f>
+        <v>0.08</v>
+      </c>
+      <c r="AH19" s="37">
+        <f>World!I17</f>
+        <v>0.02</v>
+      </c>
+      <c r="AI19" s="37">
+        <f>World!J17</f>
+        <v>0.01</v>
+      </c>
+      <c r="AJ19" s="37">
+        <f>World!K17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B20" s="21" t="s">
         <v>76</v>
       </c>
@@ -5140,23 +5497,62 @@
         <v>0.71999999999999886</v>
       </c>
       <c r="F20">
-        <f t="shared" ref="F20:H20" si="4">F19-F18</f>
+        <f t="shared" ref="F20:H20" si="7">F19-F18</f>
         <v>0.62000000000000011</v>
       </c>
       <c r="G20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0.55999999999999994</v>
       </c>
       <c r="H20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0.77999999999999403</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <f>AVERAGE(E20:H20)</f>
         <v>0.66999999999999826</v>
       </c>
-    </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="AA20" t="s">
+        <v>122</v>
+      </c>
+      <c r="AB20" s="26">
+        <f>E4</f>
+        <v>10.72</v>
+      </c>
+      <c r="AC20" s="26">
+        <f>F4</f>
+        <v>8.5399999999999991</v>
+      </c>
+      <c r="AD20" s="26">
+        <f>G4</f>
+        <v>-3.12</v>
+      </c>
+      <c r="AE20" s="26">
+        <f>H4</f>
+        <v>31.17</v>
+      </c>
+      <c r="AF20" s="26">
+        <f>I4</f>
+        <v>8.5299999999999994</v>
+      </c>
+      <c r="AG20" s="26">
+        <f>J4</f>
+        <v>31.99</v>
+      </c>
+      <c r="AH20" s="26">
+        <f>K4</f>
+        <v>-13.59</v>
+      </c>
+      <c r="AI20" s="26">
+        <f>L4</f>
+        <v>20.86</v>
+      </c>
+      <c r="AJ20" s="26">
+        <f>M4</f>
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="21" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B21" s="21" t="s">
         <v>46</v>
       </c>
@@ -5165,23 +5561,62 @@
         <v>0.27999999999999936</v>
       </c>
       <c r="F21">
-        <f t="shared" ref="F21:H21" si="5">F17-F18</f>
+        <f t="shared" ref="F21:H21" si="8">F17-F18</f>
         <v>0.30000000000000071</v>
       </c>
       <c r="G21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0.32999999999999996</v>
       </c>
       <c r="H21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0.45999999999999375</v>
       </c>
-      <c r="O21" s="26">
+      <c r="P21" s="26">
         <f>AVERAGE(E21:H21)</f>
         <v>0.34249999999999847</v>
       </c>
-    </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="AA21" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB21" s="26">
+        <f>AB16-AB17</f>
+        <v>0.13999999999999993</v>
+      </c>
+      <c r="AC21" s="26">
+        <f>AC16-AC17</f>
+        <v>0.18999999999999886</v>
+      </c>
+      <c r="AD21" s="26">
+        <f>AD16-AD17</f>
+        <v>5.999999999999972E-2</v>
+      </c>
+      <c r="AE21" s="26">
+        <f>AE16-AE17</f>
+        <v>9.0000000000001995E-2</v>
+      </c>
+      <c r="AF21" s="26">
+        <f>AF16-AF17</f>
+        <v>0.15999999999999873</v>
+      </c>
+      <c r="AG21" s="26">
+        <f>AG16-AG17</f>
+        <v>0.1</v>
+      </c>
+      <c r="AH21" s="26">
+        <f>AH16-AH17</f>
+        <v>-2.9999999999999E-2</v>
+      </c>
+      <c r="AI21" s="26">
+        <f>AI16-AI17</f>
+        <v>0.19999999999999787</v>
+      </c>
+      <c r="AJ21" s="26">
+        <f>AJ16-AJ17</f>
+        <v>0.27999999999999969</v>
+      </c>
+    </row>
+    <row r="22" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B22" s="21" t="s">
         <v>45</v>
       </c>
@@ -5190,23 +5625,23 @@
         <v>0.4399999999999995</v>
       </c>
       <c r="F22">
-        <f t="shared" ref="F22:H22" si="6">F19-F17</f>
+        <f t="shared" ref="F22:H22" si="9">F19-F17</f>
         <v>0.3199999999999994</v>
       </c>
       <c r="G22">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="H22">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0.32000000000000028</v>
       </c>
-      <c r="N22" s="28">
+      <c r="O22" s="28">
         <f>AVERAGE(E22:H22)</f>
         <v>0.32749999999999979</v>
       </c>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B25" s="21" t="s">
         <v>62</v>
       </c>
@@ -5223,7 +5658,7 @@
         <v>26.76</v>
       </c>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B26" s="21" t="s">
         <v>63</v>
       </c>
@@ -5240,7 +5675,7 @@
         <v>26.14</v>
       </c>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B27" s="21" t="s">
         <v>64</v>
       </c>
@@ -5257,7 +5692,7 @@
         <v>26.99</v>
       </c>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B28" s="21" t="s">
         <v>76</v>
       </c>
@@ -5266,23 +5701,23 @@
         <v>0.65999999999999992</v>
       </c>
       <c r="F28">
-        <f t="shared" ref="F28:H28" si="7">F27-F26</f>
+        <f t="shared" ref="F28:H28" si="10">F27-F26</f>
         <v>0.66000000000000014</v>
       </c>
       <c r="G28">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0.58999999999999986</v>
       </c>
       <c r="H28">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0.84999999999999787</v>
       </c>
-      <c r="M28">
+      <c r="N28">
         <f>AVERAGE(E28:H28)</f>
         <v>0.6899999999999995</v>
       </c>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B29" s="21" t="s">
         <v>46</v>
       </c>
@@ -5291,23 +5726,23 @@
         <v>0.57000000000000006</v>
       </c>
       <c r="F29">
-        <f t="shared" ref="F29:H29" si="8">F25-F26</f>
+        <f t="shared" ref="F29:H29" si="11">F25-F26</f>
         <v>0.48999999999999844</v>
       </c>
       <c r="G29">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0.41999999999999993</v>
       </c>
       <c r="H29">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0.62000000000000099</v>
       </c>
-      <c r="O29" s="26">
+      <c r="P29" s="26">
         <f>AVERAGE(E29:H29)</f>
         <v>0.52499999999999991</v>
       </c>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B30" s="21" t="s">
         <v>45</v>
       </c>
@@ -5316,23 +5751,23 @@
         <v>8.9999999999999858E-2</v>
       </c>
       <c r="F30">
-        <f t="shared" ref="F30:H30" si="9">F27-F25</f>
+        <f t="shared" ref="F30:H30" si="12">F27-F25</f>
         <v>0.17000000000000171</v>
       </c>
       <c r="G30">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0.16999999999999993</v>
       </c>
       <c r="H30">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0.22999999999999687</v>
       </c>
-      <c r="N30" s="28">
+      <c r="O30" s="28">
         <f>AVERAGE(E30:H30)</f>
         <v>0.16499999999999959</v>
       </c>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B33" s="21" t="s">
         <v>99</v>
       </c>
@@ -5343,7 +5778,7 @@
         <v>23.91</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B34" s="21" t="s">
         <v>100</v>
       </c>
@@ -5354,7 +5789,7 @@
         <v>24.35</v>
       </c>
     </row>
-    <row r="35" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="21" t="s">
         <v>101</v>
       </c>
@@ -5365,7 +5800,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B36" s="21" t="s">
         <v>46</v>
       </c>
@@ -5377,12 +5812,12 @@
         <f>J33-J35</f>
         <v>1.0000000000001563E-2</v>
       </c>
-      <c r="O36" s="26">
+      <c r="P36" s="26">
         <f>AVERAGE(I36:J36)</f>
         <v>8.5000000000000853E-2</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B37" s="21" t="s">
         <v>45</v>
       </c>
@@ -5394,12 +5829,12 @@
         <f>J34-J33</f>
         <v>0.44000000000000128</v>
       </c>
-      <c r="N37" s="29">
+      <c r="O37" s="29">
         <f>AVERAGE(I37:J37)</f>
         <v>0.36500000000000021</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
@@ -5407,7 +5842,7 @@
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B43" s="1"/>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
@@ -5415,12 +5850,12 @@
       <c r="F43" s="6"/>
       <c r="G43" s="6"/>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B44" s="1"/>
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
     </row>
-    <row r="49" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B49" s="1"/>
       <c r="C49" s="6"/>
       <c r="D49" s="6"/>
@@ -5428,7 +5863,7 @@
       <c r="F49" s="6"/>
       <c r="G49" s="6"/>
     </row>
-    <row r="50" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B50" s="1"/>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
@@ -5436,7 +5871,7 @@
       <c r="F50" s="6"/>
       <c r="G50" s="6"/>
     </row>
-    <row r="55" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
@@ -5444,7 +5879,7 @@
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
     </row>
-    <row r="56" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B56" s="1"/>
       <c r="C56" s="6"/>
       <c r="D56" s="6"/>
@@ -5452,14 +5887,14 @@
       <c r="F56" s="6"/>
       <c r="G56" s="6"/>
     </row>
-    <row r="57" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B57" s="1"/>
       <c r="C57" s="6"/>
       <c r="D57" s="6"/>
       <c r="E57" s="6"/>
       <c r="F57" s="6"/>
     </row>
-    <row r="60" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
@@ -5474,18 +5909,55 @@
       <c r="N60" s="1"/>
       <c r="O60" s="1"/>
       <c r="P60" s="1"/>
-    </row>
-    <row r="61" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q60" s="1"/>
+    </row>
+    <row r="61" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B61" s="1"/>
     </row>
-    <row r="62" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B62" s="1"/>
-      <c r="P62" s="26"/>
-    </row>
-    <row r="63" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q62" s="26"/>
+    </row>
+    <row r="63" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B63" s="1"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="AB20:AJ20">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB19:AJ19">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB21:AJ21">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>

--- a/NorthernTrust/NT-KostenBepaling.xlsx
+++ b/NorthernTrust/NT-KostenBepaling.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7c741cee80ec8cf3/Financieel/IndexFondsenOnderzoek/KeuzeWelkIndexFonds/OnderzoekPerFonds/NorthernTrust/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="750" documentId="13_ncr:1_{0BEEB54A-A1B5-4808-9253-8C962E6DCC11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3B76FBF-B5DA-43D1-BE16-84A1CFEFB23C}"/>
+  <xr:revisionPtr revIDLastSave="770" documentId="13_ncr:1_{0BEEB54A-A1B5-4808-9253-8C962E6DCC11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{757603FA-61CE-45CD-B00D-0ACBF722F1CE}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aannames" sheetId="4" r:id="rId1"/>
@@ -5022,8 +5022,8 @@
       <c r="N6" s="16"/>
       <c r="O6" s="16"/>
       <c r="P6" s="19">
-        <f>AVERAGE(E6:L6)</f>
-        <v>0.34999999999999937</v>
+        <f>AVERAGE(E6:M6)</f>
+        <v>0.32444444444444359</v>
       </c>
     </row>
     <row r="7" spans="2:36" x14ac:dyDescent="0.25">
@@ -5099,9 +5099,15 @@
       <c r="J10" s="22">
         <v>3.81</v>
       </c>
-      <c r="K10" s="22"/>
-      <c r="L10" s="22"/>
-      <c r="M10" s="22"/>
+      <c r="K10" s="22">
+        <v>-15.57</v>
+      </c>
+      <c r="L10" s="22">
+        <v>5.57</v>
+      </c>
+      <c r="M10" s="22">
+        <v>15.02</v>
+      </c>
       <c r="N10" s="22"/>
       <c r="O10" s="20"/>
       <c r="P10" s="22"/>
@@ -5165,9 +5171,15 @@
       <c r="J12" s="22">
         <v>3.74</v>
       </c>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="22"/>
+      <c r="K12" s="22">
+        <v>-15.59</v>
+      </c>
+      <c r="L12" s="22">
+        <v>5.89</v>
+      </c>
+      <c r="M12" s="22">
+        <v>14.95</v>
+      </c>
       <c r="N12" s="22"/>
       <c r="O12" s="20"/>
       <c r="P12" s="22"/>
@@ -5179,7 +5191,7 @@
       <c r="C13" s="22"/>
       <c r="D13" s="22"/>
       <c r="E13" s="22">
-        <f t="shared" ref="E13:J13" si="2">E10-E12</f>
+        <f t="shared" ref="E13:M13" si="2">E10-E12</f>
         <v>-0.20000000000000107</v>
       </c>
       <c r="F13" s="22">
@@ -5202,14 +5214,23 @@
         <f t="shared" si="2"/>
         <v>6.999999999999984E-2</v>
       </c>
-      <c r="K13" s="22"/>
-      <c r="L13" s="22"/>
-      <c r="M13" s="22"/>
+      <c r="K13" s="22">
+        <f t="shared" si="2"/>
+        <v>1.9999999999999574E-2</v>
+      </c>
+      <c r="L13" s="22">
+        <f t="shared" si="2"/>
+        <v>-0.3199999999999994</v>
+      </c>
+      <c r="M13" s="22">
+        <f t="shared" si="2"/>
+        <v>7.0000000000000284E-2</v>
+      </c>
       <c r="N13" s="22"/>
       <c r="O13" s="22"/>
       <c r="P13" s="22">
-        <f>AVERAGE(E13:J13)</f>
-        <v>2.4999999999999689E-2</v>
+        <f>AVERAGE(E13:M13)</f>
+        <v>-8.888888888889045E-3</v>
       </c>
       <c r="AB13" s="1">
         <f t="shared" ref="AB13:AD13" si="3">E2</f>
@@ -5224,7 +5245,7 @@
         <v>2018</v>
       </c>
       <c r="AE13" s="1">
-        <f t="shared" ref="AE13:AJ15" si="4">H2</f>
+        <f t="shared" ref="AE13:AJ14" si="4">H2</f>
         <v>2019</v>
       </c>
       <c r="AF13" s="1">
@@ -5283,7 +5304,7 @@
       <c r="M14" s="22"/>
       <c r="N14" s="22"/>
       <c r="O14" s="27">
-        <f>AVERAGE(E14:J14)</f>
+        <f>AVERAGE(E14:M14)</f>
         <v>0.36500000000000027</v>
       </c>
       <c r="P14" s="22"/>
@@ -5332,39 +5353,39 @@
         <v>123</v>
       </c>
       <c r="AB16" s="26">
-        <f>AB20-AB14</f>
+        <f t="shared" ref="AB16:AJ16" si="7">AB20-AB14</f>
         <v>0.16999999999999993</v>
       </c>
       <c r="AC16" s="26">
-        <f>AC20-AC14</f>
+        <f t="shared" si="7"/>
         <v>0.21999999999999886</v>
       </c>
       <c r="AD16" s="26">
-        <f>AD20-AD14</f>
+        <f t="shared" si="7"/>
         <v>0.17999999999999972</v>
       </c>
       <c r="AE16" s="26">
-        <f>AE20-AE14</f>
+        <f t="shared" si="7"/>
         <v>0.24000000000000199</v>
       </c>
       <c r="AF16" s="26">
-        <f>AF20-AF14</f>
+        <f t="shared" si="7"/>
         <v>0.30999999999999872</v>
       </c>
       <c r="AG16" s="26">
-        <f>AG20-AG14</f>
+        <f t="shared" si="7"/>
         <v>0.25</v>
       </c>
       <c r="AH16" s="26">
-        <f>AH20-AH14</f>
+        <f t="shared" si="7"/>
         <v>0.12000000000000099</v>
       </c>
       <c r="AI16" s="26">
-        <f>AI20-AI14</f>
+        <f t="shared" si="7"/>
         <v>0.34999999999999787</v>
       </c>
       <c r="AJ16" s="26">
-        <f>AJ20-AJ14</f>
+        <f t="shared" si="7"/>
         <v>0.42999999999999972</v>
       </c>
     </row>
@@ -5497,15 +5518,15 @@
         <v>0.71999999999999886</v>
       </c>
       <c r="F20">
-        <f t="shared" ref="F20:H20" si="7">F19-F18</f>
+        <f t="shared" ref="F20:H20" si="8">F19-F18</f>
         <v>0.62000000000000011</v>
       </c>
       <c r="G20">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.55999999999999994</v>
       </c>
       <c r="H20">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.77999999999999403</v>
       </c>
       <c r="N20">
@@ -5516,39 +5537,39 @@
         <v>122</v>
       </c>
       <c r="AB20" s="26">
-        <f>E4</f>
+        <f t="shared" ref="AB20:AJ20" si="9">E4</f>
         <v>10.72</v>
       </c>
       <c r="AC20" s="26">
-        <f>F4</f>
+        <f t="shared" si="9"/>
         <v>8.5399999999999991</v>
       </c>
       <c r="AD20" s="26">
-        <f>G4</f>
+        <f t="shared" si="9"/>
         <v>-3.12</v>
       </c>
       <c r="AE20" s="26">
-        <f>H4</f>
+        <f t="shared" si="9"/>
         <v>31.17</v>
       </c>
       <c r="AF20" s="26">
-        <f>I4</f>
+        <f t="shared" si="9"/>
         <v>8.5299999999999994</v>
       </c>
       <c r="AG20" s="26">
-        <f>J4</f>
+        <f t="shared" si="9"/>
         <v>31.99</v>
       </c>
       <c r="AH20" s="26">
-        <f>K4</f>
+        <f t="shared" si="9"/>
         <v>-13.59</v>
       </c>
       <c r="AI20" s="26">
-        <f>L4</f>
+        <f t="shared" si="9"/>
         <v>20.86</v>
       </c>
       <c r="AJ20" s="26">
-        <f>M4</f>
+        <f t="shared" si="9"/>
         <v>27.4</v>
       </c>
     </row>
@@ -5561,15 +5582,15 @@
         <v>0.27999999999999936</v>
       </c>
       <c r="F21">
-        <f t="shared" ref="F21:H21" si="8">F17-F18</f>
+        <f t="shared" ref="F21:H21" si="10">F17-F18</f>
         <v>0.30000000000000071</v>
       </c>
       <c r="G21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0.32999999999999996</v>
       </c>
       <c r="H21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0.45999999999999375</v>
       </c>
       <c r="P21" s="26">
@@ -5580,39 +5601,39 @@
         <v>126</v>
       </c>
       <c r="AB21" s="26">
-        <f>AB16-AB17</f>
+        <f t="shared" ref="AB21:AJ21" si="11">AB16-AB17</f>
         <v>0.13999999999999993</v>
       </c>
       <c r="AC21" s="26">
-        <f>AC16-AC17</f>
+        <f t="shared" si="11"/>
         <v>0.18999999999999886</v>
       </c>
       <c r="AD21" s="26">
-        <f>AD16-AD17</f>
+        <f t="shared" si="11"/>
         <v>5.999999999999972E-2</v>
       </c>
       <c r="AE21" s="26">
-        <f>AE16-AE17</f>
+        <f t="shared" si="11"/>
         <v>9.0000000000001995E-2</v>
       </c>
       <c r="AF21" s="26">
-        <f>AF16-AF17</f>
+        <f t="shared" si="11"/>
         <v>0.15999999999999873</v>
       </c>
       <c r="AG21" s="26">
-        <f>AG16-AG17</f>
+        <f t="shared" si="11"/>
         <v>0.1</v>
       </c>
       <c r="AH21" s="26">
-        <f>AH16-AH17</f>
+        <f t="shared" si="11"/>
         <v>-2.9999999999999E-2</v>
       </c>
       <c r="AI21" s="26">
-        <f>AI16-AI17</f>
+        <f t="shared" si="11"/>
         <v>0.19999999999999787</v>
       </c>
       <c r="AJ21" s="26">
-        <f>AJ16-AJ17</f>
+        <f t="shared" si="11"/>
         <v>0.27999999999999969</v>
       </c>
     </row>
@@ -5625,15 +5646,15 @@
         <v>0.4399999999999995</v>
       </c>
       <c r="F22">
-        <f t="shared" ref="F22:H22" si="9">F19-F17</f>
+        <f t="shared" ref="F22:H22" si="12">F19-F17</f>
         <v>0.3199999999999994</v>
       </c>
       <c r="G22">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="H22">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0.32000000000000028</v>
       </c>
       <c r="O22" s="28">
@@ -5701,15 +5722,15 @@
         <v>0.65999999999999992</v>
       </c>
       <c r="F28">
-        <f t="shared" ref="F28:H28" si="10">F27-F26</f>
+        <f t="shared" ref="F28:H28" si="13">F27-F26</f>
         <v>0.66000000000000014</v>
       </c>
       <c r="G28">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0.58999999999999986</v>
       </c>
       <c r="H28">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0.84999999999999787</v>
       </c>
       <c r="N28">
@@ -5726,15 +5747,15 @@
         <v>0.57000000000000006</v>
       </c>
       <c r="F29">
-        <f t="shared" ref="F29:H29" si="11">F25-F26</f>
+        <f t="shared" ref="F29:H29" si="14">F25-F26</f>
         <v>0.48999999999999844</v>
       </c>
       <c r="G29">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0.41999999999999993</v>
       </c>
       <c r="H29">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0.62000000000000099</v>
       </c>
       <c r="P29" s="26">
@@ -5751,15 +5772,15 @@
         <v>8.9999999999999858E-2</v>
       </c>
       <c r="F30">
-        <f t="shared" ref="F30:H30" si="12">F27-F25</f>
+        <f t="shared" ref="F30:H30" si="15">F27-F25</f>
         <v>0.17000000000000171</v>
       </c>
       <c r="G30">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0.16999999999999993</v>
       </c>
       <c r="H30">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0.22999999999999687</v>
       </c>
       <c r="O30" s="28">
@@ -5777,6 +5798,15 @@
       <c r="J33">
         <v>23.91</v>
       </c>
+      <c r="K33">
+        <v>-15.2</v>
+      </c>
+      <c r="L33">
+        <v>12.01</v>
+      </c>
+      <c r="M33">
+        <v>14.23</v>
+      </c>
     </row>
     <row r="34" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B34" s="21" t="s">
@@ -5799,6 +5829,15 @@
       <c r="J35">
         <v>23.9</v>
       </c>
+      <c r="K35">
+        <v>-15.41</v>
+      </c>
+      <c r="L35">
+        <v>11.86</v>
+      </c>
+      <c r="M35">
+        <v>14.11</v>
+      </c>
     </row>
     <row r="36" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B36" s="21" t="s">
@@ -5812,9 +5851,21 @@
         <f>J33-J35</f>
         <v>1.0000000000001563E-2</v>
       </c>
+      <c r="K36">
+        <f t="shared" ref="K36:M36" si="16">K33-K35</f>
+        <v>0.21000000000000085</v>
+      </c>
+      <c r="L36">
+        <f t="shared" si="16"/>
+        <v>0.15000000000000036</v>
+      </c>
+      <c r="M36">
+        <f t="shared" si="16"/>
+        <v>0.12000000000000099</v>
+      </c>
       <c r="P36" s="26">
-        <f>AVERAGE(I36:J36)</f>
-        <v>8.5000000000000853E-2</v>
+        <f>AVERAGE(I36:M36)</f>
+        <v>0.13000000000000078</v>
       </c>
     </row>
     <row r="37" spans="2:16" x14ac:dyDescent="0.25">
@@ -5830,7 +5881,7 @@
         <v>0.44000000000000128</v>
       </c>
       <c r="O37" s="29">
-        <f>AVERAGE(I37:J37)</f>
+        <f>AVERAGE(I37:M37)</f>
         <v>0.36500000000000021</v>
       </c>
     </row>
@@ -5922,8 +5973,8 @@
       <c r="B63" s="1"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="AB20:AJ20">
-    <cfRule type="colorScale" priority="4">
+  <conditionalFormatting sqref="AB19:AJ19">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5934,8 +5985,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB19:AJ19">
-    <cfRule type="colorScale" priority="3">
+  <conditionalFormatting sqref="AB20:AJ20">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/NorthernTrust/NT-KostenBepaling.xlsx
+++ b/NorthernTrust/NT-KostenBepaling.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7c741cee80ec8cf3/Financieel/IndexFondsenOnderzoek/KeuzeWelkIndexFonds/OnderzoekPerFonds/NorthernTrust/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="770" documentId="13_ncr:1_{0BEEB54A-A1B5-4808-9253-8C962E6DCC11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{757603FA-61CE-45CD-B00D-0ACBF722F1CE}"/>
+  <xr:revisionPtr revIDLastSave="980" documentId="13_ncr:1_{0BEEB54A-A1B5-4808-9253-8C962E6DCC11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17643D00-F543-4291-AC29-0991121B2796}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aannames" sheetId="4" r:id="rId1"/>
@@ -96,7 +96,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B10" authorId="0" shapeId="0" xr:uid="{566F5D12-883E-4D5B-851E-72C69E650C06}">
+    <comment ref="B13" authorId="0" shapeId="0" xr:uid="{566F5D12-883E-4D5B-851E-72C69E650C06}">
       <text>
         <r>
           <rPr>
@@ -116,11 +116,84 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-Uit 22. Portfolio Turnover Rate</t>
+Ongoing Charges Figure</t>
         </r>
       </text>
     </comment>
-    <comment ref="B12" authorId="0" shapeId="0" xr:uid="{EC001AE9-666D-4825-A5E4-EA4459FA7786}">
+    <comment ref="B16" authorId="0" shapeId="0" xr:uid="{BD1C1B9C-3BAD-45A2-992F-6823089C5EEE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>https://www.assetmanagement.hsbc.nl/en/professional-clients/fund-centre/ie00b4x9l533</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B18" authorId="1" shapeId="0" xr:uid="{0C1CBCCD-258E-4F5F-BE9F-D83596E2AAA6}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Gerben van Loon:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Pagina 159 (2023)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D30" authorId="1" shapeId="0" xr:uid="{D66E8A69-16A0-4DCC-A420-94CDCD8DEDCB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Gerben:
+A class for now since I class underperforms</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Gerben</author>
+  </authors>
+  <commentList>
+    <comment ref="B14" authorId="0" shapeId="0" xr:uid="{525B02DB-CF23-48B2-9EF4-9B279845D0C8}">
       <text>
         <r>
           <rPr>
@@ -140,80 +213,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-Uit statement of comprehensive income</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B18" authorId="0" shapeId="0" xr:uid="{BD1C1B9C-3BAD-45A2-992F-6823089C5EEE}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>https://www.assetmanagement.hsbc.nl/en/professional-clients/fund-centre/ie00b4x9l533</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B20" authorId="1" shapeId="0" xr:uid="{0C1CBCCD-258E-4F5F-BE9F-D83596E2AAA6}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Gerben van Loon:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Pagina 109 (2020)</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Gerben</author>
-  </authors>
-  <commentList>
-    <comment ref="B15" authorId="0" shapeId="0" xr:uid="{525B02DB-CF23-48B2-9EF4-9B279845D0C8}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Gerben:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-https://www.etf.hsbc.com/etf/attachments/uk/etf_december_annual_2019.pdf
-https://www.etf.hsbc.com/etf/attachments/uk/etf_december_annual_2017.pdf</t>
+https://www.assetmanagement.hsbc.co.uk/en/intermediary/funds/ie00b4x9l533?t=6</t>
         </r>
       </text>
     </comment>
@@ -227,7 +227,7 @@
     <author>Gerben van Loon</author>
   </authors>
   <commentList>
-    <comment ref="B17" authorId="0" shapeId="0" xr:uid="{19166E4E-184D-453D-824D-6D7894A37242}">
+    <comment ref="B18" authorId="0" shapeId="0" xr:uid="{19166E4E-184D-453D-824D-6D7894A37242}">
       <text>
         <r>
           <rPr>
@@ -294,6 +294,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Gerben</author>
+    <author>Gerben van Loon</author>
   </authors>
   <commentList>
     <comment ref="O2" authorId="0" shapeId="0" xr:uid="{434CD842-3C43-4334-B2E1-FAF0941512B8}">
@@ -370,7 +371,31 @@
         </r>
       </text>
     </comment>
-    <comment ref="B11" authorId="0" shapeId="0" xr:uid="{491C301F-C58A-4556-8DFB-A3897F0CAD8E}">
+    <comment ref="M9" authorId="1" shapeId="0" xr:uid="{B0D98713-8A9D-4564-A0B5-9394287A32D9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Gerben:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Huh, should be cheaper so better perf? Why worse?</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B13" authorId="0" shapeId="0" xr:uid="{491C301F-C58A-4556-8DFB-A3897F0CAD8E}">
       <text>
         <r>
           <rPr>
@@ -396,7 +421,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B35" authorId="0" shapeId="0" xr:uid="{44AC9BF2-D406-4BD8-8416-B5B9C5DDFA7D}">
+    <comment ref="B37" authorId="0" shapeId="0" xr:uid="{44AC9BF2-D406-4BD8-8416-B5B9C5DDFA7D}">
       <text>
         <r>
           <rPr>
@@ -425,7 +450,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="129">
   <si>
     <t>Transaction costs and interest expenses are excluded from the calculation.</t>
   </si>
@@ -591,9 +616,6 @@
     <t>Of in begin gewoon goedkoop geweest om vermogen aan te trekken?</t>
   </si>
   <si>
-    <t>Of de average net asset value klopt niet</t>
-  </si>
-  <si>
     <t>De in rekening gebrachte TER lijkt soms anders als wat er in rekening gebracht had moeten worden</t>
   </si>
   <si>
@@ -612,9 +634,6 @@
     <t>Northern Trust Emerging Markets Custom ESG Equity Index UCITS FGR Fund</t>
   </si>
   <si>
-    <t>Northern Trust World Custom ESG Equity Index UCITS FGR Feeder Fund</t>
-  </si>
-  <si>
     <t>Northern Trust Europe Custom ESG Equity Index UCITS FGR Feeder Fund</t>
   </si>
   <si>
@@ -735,27 +754,9 @@
     <t>WORLD SMALL CAP CUST ESG LOW CARBON Net Eur</t>
   </si>
   <si>
-    <t>Kosten</t>
-  </si>
-  <si>
     <t>Aanname 100% dividend efficient? NT antwoord daar niet op aan mij.</t>
   </si>
   <si>
-    <t>Total kosten?</t>
-  </si>
-  <si>
-    <t>% TER in rekening gebracht?</t>
-  </si>
-  <si>
-    <t>In 2020 worden ineens de transactiekosten anders berekend?</t>
-  </si>
-  <si>
-    <t>Min</t>
-  </si>
-  <si>
-    <t>Max</t>
-  </si>
-  <si>
     <t>Kosten master fonds nog los op de TER tellen of niet?</t>
   </si>
   <si>
@@ -765,30 +766,18 @@
     <t>Master: Northern Trust World Small Cap ESG Low Carbon Index FGR Fund Class F</t>
   </si>
   <si>
-    <t>Meer dan dubbele turnover in vergelijk met normaal MSCI World fonds</t>
-  </si>
-  <si>
-    <t>Schatting kosten toekomst (zonder lek)</t>
-  </si>
-  <si>
     <t>TD ruimte</t>
   </si>
   <si>
     <t>Op de 2017 factsheet adverteerde men wel met een 0.15% TER, maar factsheet TER blijft indicatie, jaarverslag is de accounting waarheid</t>
   </si>
   <si>
-    <t>Transactiekosten nogsteeds laag gezien turnover en in vergelijking met iShares/Vanguard? In 2020 wel logischer?</t>
-  </si>
-  <si>
     <t>De master fondsen lekken gewoon, de Nederlandse feeders maken dat goed. Dit zijn fiscaal transparante fondsen dus. (CCF)</t>
   </si>
   <si>
     <t>zonder master</t>
   </si>
   <si>
-    <t>met master</t>
-  </si>
-  <si>
     <t>gek, een gat?</t>
   </si>
   <si>
@@ -808,6 +797,48 @@
   </si>
   <si>
     <t>Onverklaarbaar verschil</t>
+  </si>
+  <si>
+    <t>Transactie kosten KIID</t>
+  </si>
+  <si>
+    <t>Estimated future costs</t>
+  </si>
+  <si>
+    <t>Dividend leakage</t>
+  </si>
+  <si>
+    <t>Lending</t>
+  </si>
+  <si>
+    <t>Total costs</t>
+  </si>
+  <si>
+    <t>Northern Trust World Custom ESG Equity Index UCITS FGR Feeder Fund A</t>
+  </si>
+  <si>
+    <t>Northern Trust World Custom ESG Equity Index UCITS FGR Feeder Fund I</t>
+  </si>
+  <si>
+    <t>I class</t>
+  </si>
+  <si>
+    <t>Costs</t>
+  </si>
+  <si>
+    <t>Cost range: 0,134% - 0,269%</t>
+  </si>
+  <si>
+    <t>A class</t>
+  </si>
+  <si>
+    <t>gek, een gat, wel beperkter</t>
+  </si>
+  <si>
+    <t>Cost range: 0,288% - 0,334%</t>
+  </si>
+  <si>
+    <t>Cost range: 0,328% - 0,420%</t>
   </si>
 </sst>
 </file>
@@ -932,7 +963,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -975,7 +1006,6 @@
     <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1307,15 +1337,15 @@
       <c r="B8" s="8"/>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B9" s="40" t="s">
+      <c r="B9" s="39" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B10" s="40"/>
+      <c r="B10" s="39"/>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="40"/>
+      <c r="B11" s="39"/>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B12" s="14"/>
@@ -1342,7 +1372,7 @@
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.25">
@@ -1357,7 +1387,7 @@
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.25">
@@ -1372,7 +1402,7 @@
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1386,7 +1416,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:O42"/>
+  <dimension ref="B2:O41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="36.42578125" customWidth="1"/>
@@ -1482,12 +1512,16 @@
       <c r="H5" s="11">
         <v>526476</v>
       </c>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
+      <c r="I5" s="11">
+        <v>835008</v>
+      </c>
+      <c r="J5" s="11">
+        <v>581562</v>
+      </c>
       <c r="K5" s="11"/>
       <c r="L5" s="2"/>
       <c r="O5" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.25">
@@ -1512,8 +1546,12 @@
       <c r="H6" s="11">
         <v>4671196104</v>
       </c>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
+      <c r="I6" s="11">
+        <v>5274685078</v>
+      </c>
+      <c r="J6" s="11">
+        <v>5720790174</v>
+      </c>
       <c r="K6" s="11"/>
       <c r="L6" s="2"/>
     </row>
@@ -1526,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="4">
-        <f t="shared" ref="D7:H7" si="0">D5/D6</f>
+        <f t="shared" ref="D7:J7" si="0">D5/D6</f>
         <v>0</v>
       </c>
       <c r="E7" s="4">
@@ -1545,8 +1583,14 @@
         <f t="shared" si="0"/>
         <v>1.1270689311227427E-4</v>
       </c>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
+      <c r="I7" s="4">
+        <f t="shared" si="0"/>
+        <v>1.5830480638222473E-4</v>
+      </c>
+      <c r="J7" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0165763510137087E-4</v>
+      </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="5"/>
@@ -1583,334 +1627,273 @@
         <f>'Northern Trust Master fondsen'!I6</f>
         <v>1.7136259660773064E-5</v>
       </c>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
+      <c r="I8" s="4">
+        <f>'Northern Trust Master fondsen'!J6</f>
+        <v>1.8719590320836442E-5</v>
+      </c>
+      <c r="J8" s="4">
+        <f>'Northern Trust Master fondsen'!K6</f>
+        <v>4.2184479860732762E-5</v>
+      </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="5"/>
     </row>
     <row r="9" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="4">
-        <f>SUM(C7:C8)</f>
-        <v>1.3528648432442348E-4</v>
-      </c>
-      <c r="D9" s="4">
-        <f t="shared" ref="D9:H9" si="1">SUM(D7:D8)</f>
-        <v>4.4782844092559127E-5</v>
-      </c>
-      <c r="E9" s="4">
-        <f t="shared" si="1"/>
-        <v>4.2300110328596436E-5</v>
-      </c>
-      <c r="F9" s="4">
-        <f t="shared" si="1"/>
-        <v>5.4467832522977523E-5</v>
-      </c>
-      <c r="G9" s="4">
-        <f t="shared" si="1"/>
-        <v>4.5380749412984249E-4</v>
-      </c>
-      <c r="H9" s="4">
-        <f t="shared" si="1"/>
-        <v>1.2984315277304734E-4</v>
-      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
-      <c r="M9" s="5">
-        <f>AVERAGE(C9:H9)</f>
-        <v>1.434146530285744E-4</v>
-      </c>
-      <c r="O9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="M9" s="5"/>
+    </row>
+    <row r="10" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" s="3">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="D10" s="3">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="E10" s="3">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="F10" s="3">
-        <v>1.5E-3</v>
-      </c>
-      <c r="G10" s="3">
-        <v>1.5E-3</v>
-      </c>
-      <c r="H10" s="3">
-        <v>1.5E-3</v>
-      </c>
-      <c r="I10" s="3">
-        <v>1.5E-3</v>
-      </c>
-      <c r="J10" s="3">
-        <v>1.5E-3</v>
-      </c>
-      <c r="K10" s="3">
-        <v>1.5E-3</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="C10" s="4">
+        <f>SUM(C7:C8)</f>
+        <v>1.3528648432442348E-4</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" ref="D10:J10" si="1">SUM(D7:D8)</f>
+        <v>4.4782844092559127E-5</v>
+      </c>
+      <c r="E10" s="4">
+        <f t="shared" si="1"/>
+        <v>4.2300110328596436E-5</v>
+      </c>
+      <c r="F10" s="4">
+        <f t="shared" si="1"/>
+        <v>5.4467832522977523E-5</v>
+      </c>
+      <c r="G10" s="4">
+        <f t="shared" si="1"/>
+        <v>4.5380749412984249E-4</v>
+      </c>
+      <c r="H10" s="4">
+        <f t="shared" si="1"/>
+        <v>1.2984315277304734E-4</v>
+      </c>
+      <c r="I10" s="4">
+        <f t="shared" si="1"/>
+        <v>1.7702439670306118E-4</v>
+      </c>
+      <c r="J10" s="4">
+        <f t="shared" si="1"/>
+        <v>1.4384211496210362E-4</v>
+      </c>
+      <c r="K10" s="4"/>
       <c r="L10" s="4"/>
-      <c r="M10" s="6">
-        <f>AVERAGE(C10:H10)</f>
-        <v>1.0499999999999999E-3</v>
+      <c r="M10" s="5">
+        <f>AVERAGE(C10:J10)</f>
+        <v>1.4766930372957641E-4</v>
       </c>
       <c r="O10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>115</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4">
+        <v>1E-4</v>
+      </c>
       <c r="L11" s="4"/>
-      <c r="M11" s="6"/>
-    </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" s="15">
-        <v>159521</v>
-      </c>
-      <c r="D12" s="15">
-        <f>323257-D5</f>
-        <v>323257</v>
-      </c>
-      <c r="E12" s="15">
-        <f>2280765-E5</f>
-        <v>2280765</v>
-      </c>
-      <c r="F12" s="15">
-        <f>3265001-F5</f>
-        <v>3242707</v>
-      </c>
-      <c r="G12" s="15">
-        <f>3763438-G5</f>
-        <v>2706261</v>
-      </c>
-      <c r="H12" s="15">
-        <f>4740622-H5</f>
-        <v>4214146</v>
-      </c>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
+      <c r="M11" s="5"/>
+    </row>
+    <row r="12" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
       <c r="L12" s="4"/>
-      <c r="M12" s="6"/>
-      <c r="O12" t="s">
-        <v>106</v>
-      </c>
+      <c r="M12" s="5"/>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="C13" s="3">
-        <f t="shared" ref="C13:H13" si="2">C12/C6</f>
-        <v>2.6266407285764366E-4</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="D13" s="3">
-        <f t="shared" si="2"/>
-        <v>2.8077493451108816E-4</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="E13" s="3">
-        <f t="shared" si="2"/>
-        <v>1.2805674672750266E-3</v>
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="F13" s="3">
-        <f t="shared" si="2"/>
-        <v>1.212749278510918E-3</v>
+        <v>1.5E-3</v>
       </c>
       <c r="G13" s="3">
-        <f t="shared" si="2"/>
-        <v>1.0026764117315734E-3</v>
+        <v>1.5E-3</v>
       </c>
       <c r="H13" s="3">
-        <f t="shared" si="2"/>
-        <v>9.0215565910225376E-4</v>
-      </c>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
+        <v>1.5E-3</v>
+      </c>
+      <c r="I13" s="3">
+        <v>1.5E-3</v>
+      </c>
+      <c r="J13" s="3">
+        <v>1.5E-3</v>
+      </c>
       <c r="K13" s="3"/>
       <c r="L13" s="4"/>
       <c r="M13" s="6">
-        <f>AVERAGE(C13:H13)</f>
-        <v>8.2359797066475053E-4</v>
-      </c>
-      <c r="O13" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>102</v>
-      </c>
+        <f>AVERAGE(C13:J13)</f>
+        <v>1.1624999999999999E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C14" s="3"/>
-      <c r="D14" s="15">
-        <f>D12+D5</f>
-        <v>323257</v>
-      </c>
-      <c r="E14" s="15">
-        <f t="shared" ref="E14:H14" si="3">E12+E5</f>
-        <v>2280765</v>
-      </c>
-      <c r="F14" s="15">
-        <f t="shared" si="3"/>
-        <v>3265001</v>
-      </c>
-      <c r="G14" s="15">
-        <f t="shared" si="3"/>
-        <v>3763438</v>
-      </c>
-      <c r="H14" s="15">
-        <f t="shared" si="3"/>
-        <v>4740622</v>
-      </c>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
       <c r="L14" s="4"/>
       <c r="M14" s="6"/>
-      <c r="O14" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>104</v>
-      </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3">
-        <f>D14/D6</f>
-        <v>2.8077493451108816E-4</v>
-      </c>
-      <c r="E15" s="3">
-        <f t="shared" ref="E15:H15" si="4">E14/E6</f>
-        <v>1.2805674672750266E-3</v>
-      </c>
-      <c r="F15" s="3">
-        <f t="shared" si="4"/>
-        <v>1.2210870754241522E-3</v>
-      </c>
-      <c r="G15" s="3">
-        <f t="shared" si="4"/>
-        <v>1.3943631119150183E-3</v>
-      </c>
-      <c r="H15" s="3">
-        <f t="shared" si="4"/>
-        <v>1.0148625522145281E-3</v>
-      </c>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="6"/>
-    </row>
-    <row r="16" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="6"/>
-      <c r="O16" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="17" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>91</v>
-      </c>
-      <c r="C17" s="24">
+        <v>89</v>
+      </c>
+      <c r="C15" s="24">
         <f>0.07</f>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="D17" s="24">
+      <c r="D15" s="24">
         <f>0.01</f>
         <v>0.01</v>
       </c>
-      <c r="E17" s="24">
+      <c r="E15" s="24">
         <f>0.09</f>
         <v>0.09</v>
       </c>
-      <c r="F17" s="24">
+      <c r="F15" s="24">
         <f>0.26</f>
         <v>0.26</v>
       </c>
-      <c r="G17" s="24">
+      <c r="G15" s="24">
         <v>0.19</v>
       </c>
-      <c r="H17" s="24">
+      <c r="H15" s="24">
         <v>0.08</v>
       </c>
-      <c r="I17" s="24">
+      <c r="I15" s="24">
         <v>0.02</v>
       </c>
-      <c r="J17" s="24">
+      <c r="J15" s="24">
         <v>0.01</v>
       </c>
-      <c r="K17" s="24"/>
+      <c r="K15" s="24"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="37">
+        <f>AVERAGE(E15:J15)</f>
+        <v>0.10833333333333334</v>
+      </c>
+      <c r="N15" s="4"/>
+    </row>
+    <row r="16" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" s="24">
+        <v>0.1464</v>
+      </c>
+      <c r="D16" s="24">
+        <v>5.3100000000000001E-2</v>
+      </c>
+      <c r="E16" s="24">
+        <v>0.1013</v>
+      </c>
+      <c r="F16" s="24">
+        <v>9.2600000000000002E-2</v>
+      </c>
+      <c r="G16" s="24">
+        <v>3.32E-2</v>
+      </c>
+      <c r="H16" s="24">
+        <v>7.9200000000000007E-2</v>
+      </c>
+      <c r="I16" s="24">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="J16" s="24">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="K16" s="24"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="37">
+        <f>AVERAGE(E16:J16)</f>
+        <v>6.7549999999999999E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
       <c r="L17" s="4"/>
-      <c r="M17" s="37">
-        <f>AVERAGE(E17:H17)</f>
-        <v>0.155</v>
-      </c>
-      <c r="N17" s="4"/>
-    </row>
-    <row r="18" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M17" s="5"/>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>96</v>
-      </c>
-      <c r="C18" s="24">
-        <v>0.1464</v>
-      </c>
-      <c r="D18" s="24">
-        <v>5.3100000000000001E-2</v>
-      </c>
-      <c r="E18" s="24">
-        <v>0.1013</v>
-      </c>
-      <c r="F18" s="24">
-        <v>9.2600000000000002E-2</v>
-      </c>
-      <c r="G18" s="24">
-        <v>3.32E-2</v>
-      </c>
-      <c r="H18" s="24">
-        <v>7.9200000000000007E-2</v>
-      </c>
-      <c r="I18" s="24"/>
-      <c r="J18" s="24"/>
-      <c r="K18" s="24"/>
+        <v>102</v>
+      </c>
+      <c r="C18" s="25"/>
+      <c r="D18" s="4"/>
+      <c r="F18" s="3">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="G18" s="3">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="H18" s="3">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="I18" s="3">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="J18" s="3">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="K18" s="3"/>
       <c r="L18" s="4"/>
-      <c r="M18" s="37">
-        <f>AVERAGE(E18:H18)</f>
-        <v>7.6575000000000004E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M18" s="5">
+        <f>AVERAGE(F18:J18)</f>
+        <v>2.9999999999999997E-4</v>
+      </c>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C19" s="3"/>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
@@ -1924,31 +1907,36 @@
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>110</v>
-      </c>
-      <c r="C20" s="25"/>
-      <c r="D20" s="4"/>
-      <c r="F20" s="4">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="G20" s="3">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="H20" s="3">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="C20" s="6">
+        <f>M10+M13</f>
+        <v>1.3101693037295763E-3</v>
+      </c>
+      <c r="D20" t="s">
+        <v>107</v>
+      </c>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
       <c r="L20" s="4"/>
-      <c r="M20" s="5">
-        <f>AVERAGE(F20:H20)</f>
-        <v>2.9999999999999997E-4</v>
-      </c>
+      <c r="M20" s="5"/>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C21" s="3"/>
-      <c r="D21" s="4"/>
+      <c r="B21" t="s">
+        <v>104</v>
+      </c>
+      <c r="C21" s="6">
+        <f>('Tracking Difference'!O7/100)-C20</f>
+        <v>1.2120529184926432E-3</v>
+      </c>
+      <c r="D21" t="s">
+        <v>108</v>
+      </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
@@ -1960,16 +1948,7 @@
       <c r="M21" s="5"/>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>82</v>
-      </c>
-      <c r="C22" s="6">
-        <f>M9+M13</f>
-        <v>9.6701262369332491E-4</v>
-      </c>
-      <c r="D22" t="s">
-        <v>118</v>
-      </c>
+      <c r="C22" s="6"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
@@ -1981,16 +1960,7 @@
       <c r="M22" s="5"/>
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
-        <v>114</v>
-      </c>
-      <c r="C23" s="6">
-        <f>('Tracking Difference'!O7/100)-C22</f>
-        <v>1.5552095985288945E-3</v>
-      </c>
-      <c r="D23" t="s">
-        <v>120</v>
-      </c>
+      <c r="C23" s="6"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
@@ -2002,7 +1972,9 @@
       <c r="M23" s="5"/>
     </row>
     <row r="24" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C24" s="6"/>
+      <c r="B24" s="1" t="s">
+        <v>116</v>
+      </c>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
@@ -2014,15 +1986,12 @@
       <c r="M24" s="5"/>
     </row>
     <row r="25" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B25" t="s">
-        <v>82</v>
-      </c>
-      <c r="C25" s="6">
-        <f>M9+M13+M20</f>
-        <v>1.2670126236933249E-3</v>
-      </c>
-      <c r="D25" t="s">
-        <v>119</v>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
@@ -2036,16 +2005,14 @@
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C26" s="6">
-        <f>('Tracking Difference'!O7/100)-C25</f>
-        <v>1.2552095985288946E-3</v>
-      </c>
-      <c r="D26" t="s">
-        <v>120</v>
-      </c>
-      <c r="E26" s="4"/>
+        <v>1E-3</v>
+      </c>
+      <c r="E26" t="s">
+        <v>122</v>
+      </c>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
@@ -2056,7 +2023,13 @@
       <c r="M26" s="5"/>
     </row>
     <row r="27" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C27" s="6"/>
+      <c r="B27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="5">
+        <f>AVERAGE(I10:J10)</f>
+        <v>1.6043325583258241E-4</v>
+      </c>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
@@ -2068,6 +2041,13 @@
       <c r="M27" s="5"/>
     </row>
     <row r="28" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>117</v>
+      </c>
+      <c r="C28" s="6">
+        <f>AVERAGE(0.42%,1.05%)*2.5%</f>
+        <v>1.8375000000000002E-4</v>
+      </c>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
@@ -2079,7 +2059,13 @@
       <c r="M28" s="5"/>
     </row>
     <row r="29" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C29" s="6"/>
+      <c r="B29" t="s">
+        <v>118</v>
+      </c>
+      <c r="C29" s="5">
+        <v>0</v>
+      </c>
+      <c r="D29" s="4"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
@@ -2089,41 +2075,38 @@
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
       <c r="M29" s="5"/>
+      <c r="O29" s="3"/>
     </row>
     <row r="30" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C30" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4"/>
-      <c r="K30" s="4"/>
+      <c r="B30" t="s">
+        <v>119</v>
+      </c>
+      <c r="C30" s="5">
+        <f>SUM(C26:C29)</f>
+        <v>1.3441832558325824E-3</v>
+      </c>
+      <c r="D30" s="4">
+        <f>AVERAGE('Tracking Difference'!G7:M7)/100</f>
+        <v>2.6857142857142839E-3</v>
+      </c>
       <c r="L30" s="4"/>
       <c r="M30" s="5"/>
-      <c r="O30" s="3"/>
     </row>
     <row r="31" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B31" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C31" s="6">
-        <f>H10+H9</f>
-        <v>1.6298431527730474E-3</v>
-      </c>
-      <c r="D31" s="3">
-        <f>C31+H20</f>
-        <v>1.9298431527730473E-3</v>
-      </c>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
       <c r="L31" s="4"/>
       <c r="M31" s="5"/>
     </row>
     <row r="32" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>124</v>
+      </c>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
@@ -2135,6 +2118,7 @@
       <c r="M32" s="5"/>
     </row>
     <row r="33" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C33" s="6"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
@@ -2156,23 +2140,21 @@
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
       <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
     </row>
     <row r="35" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C35" s="6"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="4"/>
-      <c r="L35" s="4"/>
-      <c r="M35" s="5"/>
-      <c r="N35" s="5"/>
+      <c r="C35" s="32"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="32"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="32"/>
+      <c r="J35" s="32"/>
+      <c r="K35" s="32"/>
     </row>
     <row r="36" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C36" s="32"/>
-      <c r="D36" s="32"/>
+      <c r="C36" s="6"/>
       <c r="E36" s="32"/>
       <c r="F36" s="32"/>
       <c r="G36" s="32"/>
@@ -2182,7 +2164,8 @@
       <c r="K36" s="32"/>
     </row>
     <row r="37" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C37" s="6"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
       <c r="E37" s="32"/>
       <c r="F37" s="32"/>
       <c r="G37" s="32"/>
@@ -2192,8 +2175,8 @@
       <c r="K37" s="32"/>
     </row>
     <row r="38" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
+      <c r="C38" s="38"/>
+      <c r="D38" s="38"/>
       <c r="E38" s="32"/>
       <c r="F38" s="32"/>
       <c r="G38" s="32"/>
@@ -2203,27 +2186,16 @@
       <c r="K38" s="32"/>
     </row>
     <row r="39" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C39" s="39"/>
-      <c r="D39" s="39"/>
-      <c r="E39" s="32"/>
-      <c r="F39" s="32"/>
-      <c r="G39" s="32"/>
-      <c r="H39" s="32"/>
-      <c r="I39" s="32"/>
-      <c r="J39" s="32"/>
-      <c r="K39" s="32"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
     </row>
     <row r="40" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
+      <c r="D40" s="3"/>
     </row>
     <row r="41" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C41" s="6"/>
-      <c r="D41" s="3"/>
-    </row>
-    <row r="42" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C42" s="24"/>
-      <c r="D42" s="6"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2234,18 +2206,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F5B4C98-CE28-4015-A5EF-F840D4E9DB1C}">
-  <dimension ref="B2:L37"/>
+  <dimension ref="B2:O34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="37.7109375" customWidth="1"/>
-    <col min="3" max="8" width="17.7109375" customWidth="1"/>
-    <col min="9" max="9" width="6.140625" customWidth="1"/>
-    <col min="10" max="10" width="13.28515625" customWidth="1"/>
-    <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="91.85546875" customWidth="1"/>
+    <col min="3" max="11" width="17.7109375" customWidth="1"/>
+    <col min="12" max="12" width="6.140625" customWidth="1"/>
+    <col min="13" max="13" width="13.28515625" customWidth="1"/>
+    <col min="14" max="14" width="18" customWidth="1"/>
+    <col min="15" max="15" width="91.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B2" s="10" t="s">
         <v>2</v>
       </c>
@@ -2257,19 +2229,22 @@
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
-      <c r="L2" s="1" t="s">
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="O2" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>22</v>
       </c>
-      <c r="L3" t="s">
+      <c r="O3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C4" s="1">
         <v>2016</v>
       </c>
@@ -2288,15 +2263,24 @@
       <c r="H4" s="1">
         <v>2021</v>
       </c>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1" t="s">
+      <c r="I4" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J4" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K4" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L4" t="s">
+      <c r="O4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>1</v>
       </c>
@@ -2318,9 +2302,16 @@
       <c r="H5" s="2">
         <v>1944889</v>
       </c>
-      <c r="I5" s="2"/>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="I5" s="2">
+        <v>2383697</v>
+      </c>
+      <c r="J5" s="2">
+        <v>3009690</v>
+      </c>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>7</v>
       </c>
@@ -2342,364 +2333,420 @@
       <c r="H6" s="2">
         <v>3883272002</v>
       </c>
-      <c r="I6" s="2"/>
-      <c r="L6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
+      <c r="I6" s="2">
+        <v>4414212937</v>
+      </c>
+      <c r="J6" s="2">
+        <v>4551400032</v>
+      </c>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="O6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C8" s="3">
         <f>C5/C6</f>
         <v>6.6379643974936542E-4</v>
       </c>
-      <c r="D7" s="3">
-        <f t="shared" ref="D7:H7" si="0">D5/D6</f>
+      <c r="D8" s="3">
+        <f t="shared" ref="D8:J8" si="0">D5/D6</f>
         <v>9.8516679690304203E-4</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E8" s="3">
         <f t="shared" si="0"/>
         <v>2.9372498591450741E-4</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F8" s="3">
         <f t="shared" si="0"/>
         <v>4.4199311030115364E-4</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G8" s="4">
         <f t="shared" si="0"/>
         <v>5.26040873999595E-4</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H8" s="4">
         <f t="shared" si="0"/>
         <v>5.008376953760449E-4</v>
       </c>
-      <c r="I7" s="4"/>
-      <c r="J7" s="6">
-        <f>AVERAGE(C7:H7)</f>
-        <v>5.6859331704061809E-4</v>
-      </c>
-      <c r="K7" s="3"/>
-    </row>
-    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" s="6">
+      <c r="I8" s="4">
+        <f t="shared" si="0"/>
+        <v>5.4000498707704279E-4</v>
+      </c>
+      <c r="J8" s="4">
+        <f t="shared" si="0"/>
+        <v>6.6126685829403272E-4</v>
+      </c>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="6">
+        <f>AVERAGE(C8:J8)</f>
+        <v>5.7660396845184809E-4</v>
+      </c>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="L9" s="4"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="6">
         <v>2.8E-3</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D11" s="6">
         <v>2E-3</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E11" s="6">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F11" s="6">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G11" s="6">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H11" s="6">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="6">
-        <f>AVERAGE(C8:H8)</f>
-        <v>2.4666666666666669E-3</v>
-      </c>
-      <c r="L8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="6"/>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" s="2">
-        <f>252128-C5</f>
-        <v>203782</v>
-      </c>
-      <c r="D10" s="2">
-        <f>842623-D5</f>
-        <v>565933</v>
-      </c>
-      <c r="E10" s="2">
-        <f>2541872-E5</f>
-        <v>2307298</v>
-      </c>
-      <c r="F10" s="2">
-        <f>4524697-F5</f>
-        <v>3852014</v>
-      </c>
-      <c r="G10" s="2">
-        <f>6441892-G5</f>
-        <v>5152610</v>
-      </c>
-      <c r="H10" s="2">
-        <f>9439821-H5</f>
-        <v>7494932</v>
-      </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="6"/>
-      <c r="L10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
+      <c r="I11" s="6">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="J11" s="6">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="K11" s="6"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="6">
+        <f>AVERAGE(C11:J11)</f>
+        <v>2.4750000000000002E-3</v>
+      </c>
+      <c r="O11" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="3">
-        <f>C10/C6</f>
-        <v>2.7979515592811231E-3</v>
-      </c>
-      <c r="D11" s="3">
-        <f>D10/D6</f>
-        <v>2.0150290970824001E-3</v>
-      </c>
-      <c r="E11" s="3">
-        <f t="shared" ref="E11:H11" si="1">E10/E6</f>
-        <v>2.8891141923255395E-3</v>
-      </c>
-      <c r="F11" s="3">
-        <f t="shared" si="1"/>
-        <v>2.5310044237532212E-3</v>
-      </c>
-      <c r="G11" s="3">
-        <f t="shared" si="1"/>
-        <v>2.1023201035762951E-3</v>
-      </c>
-      <c r="H11" s="3">
-        <f t="shared" si="1"/>
-        <v>1.9300558900174616E-3</v>
-      </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="6">
-        <f>AVERAGE(C11:H11)</f>
-        <v>2.3775792110060068E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="2"/>
+    </row>
+    <row r="12" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
       <c r="J12" s="6"/>
-      <c r="L12" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="K12" s="6"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="6"/>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>95</v>
-      </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3">
-        <v>1E-4</v>
-      </c>
-      <c r="F13" s="3">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="6"/>
-      <c r="L13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>91</v>
-      </c>
-      <c r="C14" s="24">
+        <v>89</v>
+      </c>
+      <c r="C13" s="24">
         <f>1.53</f>
         <v>1.53</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D13" s="24">
         <f>1.09</f>
         <v>1.0900000000000001</v>
       </c>
-      <c r="E14" s="24">
+      <c r="E13" s="24">
         <f>0.46</f>
         <v>0.46</v>
       </c>
-      <c r="F14" s="24">
+      <c r="F13" s="24">
         <f>0.13</f>
         <v>0.13</v>
       </c>
+      <c r="G13" s="24">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="H13" s="24">
+        <v>0.02</v>
+      </c>
+      <c r="I13" s="37">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="J13" s="24">
+        <v>0.01</v>
+      </c>
+      <c r="K13" s="24"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="37">
+        <f>AVERAGE(C13:J13)</f>
+        <v>0.54749999999999999</v>
+      </c>
+      <c r="N13" s="3"/>
+      <c r="O13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C14" s="24">
+        <v>0.1845</v>
+      </c>
+      <c r="D14" s="24">
+        <v>2.6200000000000001E-2</v>
+      </c>
+      <c r="E14" s="24">
+        <v>7.3300000000000004E-2</v>
+      </c>
+      <c r="F14" s="24">
+        <v>0.2301</v>
+      </c>
       <c r="G14" s="24">
-        <v>0.56999999999999995</v>
+        <v>1.7081</v>
       </c>
       <c r="H14" s="24">
-        <v>0.02</v>
-      </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="37">
-        <f>AVERAGE(C14:H14)</f>
-        <v>0.6333333333333333</v>
-      </c>
-      <c r="K14" s="3"/>
-      <c r="L14" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>98</v>
-      </c>
-      <c r="C15" s="24">
-        <v>0.1845</v>
-      </c>
-      <c r="D15" s="24">
-        <v>2.6200000000000001E-2</v>
-      </c>
-      <c r="E15" s="24">
-        <v>7.3300000000000004E-2</v>
-      </c>
-      <c r="F15" s="24">
-        <v>0.2301</v>
-      </c>
-      <c r="G15" s="24">
-        <v>1.7081</v>
-      </c>
-      <c r="H15" s="24">
         <v>0.2447</v>
       </c>
-      <c r="I15" s="2"/>
-      <c r="J15" s="37">
-        <f>AVERAGE(C15:H15)</f>
-        <v>0.41114999999999996</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="5"/>
-      <c r="L16" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="17" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I14" s="24">
+        <v>8.6999999999999994E-3</v>
+      </c>
+      <c r="J14" s="6">
+        <v>0.1177</v>
+      </c>
+      <c r="K14" s="6"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="37">
+        <f>AVERAGE(C14:J14)</f>
+        <v>0.32416250000000002</v>
+      </c>
+      <c r="O14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="5"/>
+      <c r="O15" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" s="6">
+        <f>M8+M11</f>
+        <v>3.0516039684518482E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="C17" s="6">
-        <f>J7+J11</f>
-        <v>2.946172528046625E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C18" s="25">
-        <f>H8+H7</f>
-        <v>3.0008376953760451E-3</v>
-      </c>
-    </row>
-    <row r="19" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <f>('Tracking Difference'!O16/100)-C16</f>
+        <v>1.1483960315481524E-3</v>
+      </c>
+      <c r="D17" t="s">
+        <v>108</v>
+      </c>
+      <c r="O17" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C18" s="6"/>
+    </row>
+    <row r="19" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C19" s="6"/>
       <c r="D19" s="4"/>
     </row>
-    <row r="20" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
-        <v>114</v>
-      </c>
-      <c r="C20" s="6">
-        <f>('Tracking Difference'!O14/100)-C17</f>
-        <v>7.0382747195337761E-4</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D21" s="4"/>
-    </row>
-    <row r="22" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="1"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="38"/>
-    </row>
-    <row r="23" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="1"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="4"/>
-    </row>
-    <row r="24" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C24" s="25"/>
-      <c r="D24" s="4"/>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B25" s="1"/>
-      <c r="C25" s="25"/>
+    <row r="20" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="1"/>
+      <c r="C21" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>113</v>
+      </c>
+      <c r="C22" s="6">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="E22" t="s">
+        <v>125</v>
+      </c>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="5"/>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" s="5">
+        <f>AVERAGE(I8:J8)</f>
+        <v>6.0063592268553775E-4</v>
+      </c>
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>117</v>
+      </c>
+      <c r="C24" s="6">
+        <f>AVERAGE(0.42%,1.05%)*2.5%</f>
+        <v>1.8375000000000002E-4</v>
+      </c>
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>118</v>
+      </c>
+      <c r="C25" s="5">
+        <v>0</v>
+      </c>
+      <c r="D25" s="4"/>
       <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="5"/>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>119</v>
+      </c>
+      <c r="C26" s="5">
+        <f>SUM(C22:C25)</f>
+        <v>3.2843859226855377E-3</v>
+      </c>
+      <c r="D26" s="4">
+        <f>'Tracking Difference'!O16/100</f>
+        <v>4.2000000000000006E-3</v>
+      </c>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="32"/>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="E27" s="4"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="32"/>
+      <c r="J27" s="32"/>
+      <c r="K27" s="32"/>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>128</v>
+      </c>
+      <c r="E28" s="4"/>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C29" s="32"/>
       <c r="D29" s="32"/>
       <c r="E29" s="32"/>
       <c r="F29" s="32"/>
       <c r="G29" s="32"/>
       <c r="H29" s="32"/>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I29" s="32"/>
+      <c r="J29" s="32"/>
+      <c r="K29" s="32"/>
+    </row>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C30" s="32"/>
       <c r="D30" s="32"/>
       <c r="E30" s="32"/>
       <c r="F30" s="32"/>
       <c r="G30" s="32"/>
       <c r="H30" s="32"/>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C32" s="32"/>
-      <c r="D32" s="32"/>
-      <c r="E32" s="32"/>
-      <c r="F32" s="32"/>
-      <c r="G32" s="32"/>
-      <c r="H32" s="32"/>
-    </row>
-    <row r="33" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C33" s="32"/>
-      <c r="D33" s="32"/>
-      <c r="E33" s="32"/>
-      <c r="F33" s="32"/>
-      <c r="G33" s="32"/>
-      <c r="H33" s="32"/>
-    </row>
-    <row r="34" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C34" s="32"/>
-      <c r="D34" s="32"/>
-      <c r="E34" s="32"/>
-      <c r="F34" s="32"/>
-      <c r="G34" s="32"/>
-      <c r="H34" s="32"/>
-    </row>
-    <row r="37" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C37" s="24"/>
+      <c r="I30" s="32"/>
+      <c r="J30" s="32"/>
+      <c r="K30" s="32"/>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C31" s="32"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="32"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="32"/>
+      <c r="J31" s="32"/>
+      <c r="K31" s="32"/>
+    </row>
+    <row r="34" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C34" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2710,18 +2757,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9123B064-D487-424B-955E-970CD2CDF897}">
-  <dimension ref="B2:L37"/>
+  <dimension ref="B2:O34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="36.42578125" customWidth="1"/>
-    <col min="3" max="8" width="17.7109375" customWidth="1"/>
-    <col min="9" max="9" width="6.140625" customWidth="1"/>
-    <col min="10" max="10" width="13.28515625" customWidth="1"/>
-    <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="91.85546875" customWidth="1"/>
+    <col min="3" max="11" width="17.7109375" customWidth="1"/>
+    <col min="12" max="12" width="6.140625" customWidth="1"/>
+    <col min="13" max="13" width="13.28515625" customWidth="1"/>
+    <col min="14" max="14" width="18" customWidth="1"/>
+    <col min="15" max="15" width="91.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B2" s="10" t="s">
         <v>9</v>
       </c>
@@ -2733,16 +2780,19 @@
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
-      <c r="L2" s="1" t="s">
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="O2" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C4" s="1">
         <v>2016</v>
       </c>
@@ -2761,12 +2811,21 @@
       <c r="H4" s="1">
         <v>2021</v>
       </c>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1" t="s">
+      <c r="I4" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J4" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K4" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>1</v>
       </c>
@@ -2782,9 +2841,16 @@
       <c r="H5" s="2">
         <v>203240</v>
       </c>
-      <c r="I5" s="2"/>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="I5" s="2">
+        <v>176525</v>
+      </c>
+      <c r="J5" s="2">
+        <v>225040</v>
+      </c>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>7</v>
       </c>
@@ -2800,9 +2866,16 @@
       <c r="H6" s="2">
         <v>536989210</v>
       </c>
-      <c r="I6" s="2"/>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="I6" s="2">
+        <v>637533337</v>
+      </c>
+      <c r="J6" s="2">
+        <v>881262286</v>
+      </c>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>8</v>
       </c>
@@ -2820,204 +2893,329 @@
         <f>H5/H6</f>
         <v>3.7848060299014202E-4</v>
       </c>
-      <c r="I7" s="4"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="3"/>
-    </row>
-    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I7" s="4">
+        <f t="shared" ref="I7:J7" si="0">I5/I6</f>
+        <v>2.7688748141495225E-4</v>
+      </c>
+      <c r="J7" s="4">
+        <f t="shared" si="0"/>
+        <v>2.5536097887661111E-4</v>
+      </c>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="3"/>
+    </row>
+    <row r="8" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>16</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3">
-        <f>'Northern Trust Master fondsen'!G22</f>
+        <f>'Northern Trust Master fondsen'!G20</f>
         <v>8.9319673455790307E-4</v>
       </c>
       <c r="G8" s="3">
-        <f>'Northern Trust Master fondsen'!H22</f>
+        <f>'Northern Trust Master fondsen'!H20</f>
         <v>3.2934847239067549E-4</v>
       </c>
       <c r="H8" s="3">
-        <f>'Northern Trust Master fondsen'!I22</f>
+        <f>'Northern Trust Master fondsen'!I20</f>
         <v>1.5612069852104837E-4</v>
       </c>
-      <c r="I8" s="4"/>
-      <c r="J8" s="6"/>
-    </row>
-    <row r="9" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
+      <c r="I8" s="3">
+        <f>'Northern Trust Master fondsen'!J20</f>
+        <v>1.6460527385106098E-4</v>
+      </c>
+      <c r="J8" s="3">
+        <f>'Northern Trust Master fondsen'!K20</f>
+        <v>1.0025390999295887E-4</v>
+      </c>
+      <c r="K8" s="3"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="6"/>
+    </row>
+    <row r="9" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
-      <c r="F9" s="3">
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="6"/>
+    </row>
+    <row r="10" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3">
         <f>SUM(F7:F8)</f>
         <v>9.0901882940875559E-4</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G10" s="4">
         <f>SUM(G7:G8)</f>
         <v>9.9518385707461805E-4</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H10" s="4">
         <f>SUM(H7:H8)</f>
         <v>5.3460130151119036E-4</v>
       </c>
-      <c r="I9" s="4"/>
-      <c r="J9" s="6">
-        <f>AVERAGE(G9:H9)</f>
-        <v>7.6489257929290421E-4</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>71</v>
-      </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="6">
-        <v>2.3E-3</v>
-      </c>
-      <c r="G10" s="6">
-        <v>2.3E-3</v>
-      </c>
-      <c r="H10" s="6">
-        <v>2.2000000000000001E-3</v>
-      </c>
-      <c r="J10" s="6">
-        <f>AVERAGE(G10:H10)</f>
-        <v>2.2500000000000003E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="J11" s="6"/>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>67</v>
-      </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2">
-        <f>108396-F5</f>
-        <v>106265</v>
-      </c>
-      <c r="G12" s="2">
-        <f>404158-G5</f>
-        <v>264380</v>
-      </c>
-      <c r="H12" s="2">
-        <f>1012274-H5</f>
-        <v>809034</v>
-      </c>
-      <c r="J12" s="6"/>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="I10" s="4">
+        <f t="shared" ref="I10:J10" si="1">SUM(I7:I8)</f>
+        <v>4.4149275526601323E-4</v>
+      </c>
+      <c r="J10" s="4">
+        <f t="shared" si="1"/>
+        <v>3.5561488886956999E-4</v>
+      </c>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="6">
+        <f>AVERAGE(G10:J10)</f>
+        <v>5.8172320068034791E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>115</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="L11" s="4"/>
+      <c r="M11" s="6"/>
+    </row>
+    <row r="12" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="6"/>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
-      <c r="F13" s="3">
-        <f>F12/F6</f>
-        <v>7.889886951317909E-4</v>
-      </c>
-      <c r="G13" s="3">
-        <f>G12/G6</f>
-        <v>1.2593795804972225E-3</v>
-      </c>
-      <c r="H13" s="3">
-        <f>H12/H6</f>
-        <v>1.5066112780925337E-3</v>
+      <c r="F13" s="6">
+        <v>2.3E-3</v>
+      </c>
+      <c r="G13" s="6">
+        <v>2.3E-3</v>
+      </c>
+      <c r="H13" s="6">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="I13" s="6">
+        <v>2.3E-3</v>
       </c>
       <c r="J13" s="6">
-        <f>AVERAGE(G13:H13)</f>
-        <v>1.382995429294878E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>91</v>
-      </c>
-      <c r="F15" s="37">
+        <v>2.3E-3</v>
+      </c>
+      <c r="K13" s="6"/>
+      <c r="M13" s="6">
+        <f>AVERAGE(G13:J13)</f>
+        <v>2.2750000000000001E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="M14" s="6"/>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>89</v>
+      </c>
+      <c r="F16" s="37">
         <f>0.01</f>
         <v>0.01</v>
       </c>
-      <c r="G15" s="37">
+      <c r="G16" s="37">
         <v>0.17</v>
       </c>
-      <c r="H15" s="37">
+      <c r="H16" s="37">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="F16" s="37"/>
-      <c r="G16" s="37"/>
-      <c r="H16" s="37"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F17" s="6">
+      <c r="I16" s="37">
+        <v>0.09</v>
+      </c>
+      <c r="J16" s="37">
+        <v>0.05</v>
+      </c>
+      <c r="K16" s="37"/>
+      <c r="M16" s="37">
+        <f>AVERAGE(G16:J16)</f>
+        <v>0.10249999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="F17" s="37"/>
+      <c r="G17" s="37"/>
+      <c r="H17" s="37"/>
+      <c r="I17" s="37"/>
+      <c r="J17" s="37"/>
+      <c r="K17" s="37"/>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B18" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F18" s="6">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G18" s="6">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="H17" s="6">
+      <c r="H18" s="6">
         <v>2.9999999999999997E-4</v>
       </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" s="6">
-        <f>J9+J10</f>
-        <v>3.0148925792929044E-3</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C21" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="1" t="s">
+      <c r="I18" s="6">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="J18" s="6">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="K18" s="6"/>
+      <c r="M18" s="6">
+        <f>AVERAGE(G18:J18)</f>
+        <v>3.5E-4</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="6">
+        <f>M10+M13</f>
+        <v>2.856723200680348E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>104</v>
+      </c>
+      <c r="C21" s="6">
+        <f>('Tracking Difference'!O39/100)-C20</f>
+        <v>4.8327679931965163E-4</v>
+      </c>
+      <c r="D21" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C22" s="3"/>
+      <c r="D22" s="4"/>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B24" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B25" s="1"/>
+      <c r="C25" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" s="4"/>
+    </row>
+    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
         <v>113</v>
       </c>
-      <c r="C22" s="6">
-        <f>H9+H10</f>
-        <v>2.7346013015111907E-3</v>
-      </c>
-      <c r="D22" s="3">
-        <f>C22+H17</f>
-        <v>3.0346013015111906E-3</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
-        <v>114</v>
-      </c>
-      <c r="C24" s="6">
-        <f>('Tracking Difference'!O30/100)-C19</f>
-        <v>-1.3648925792929085E-3</v>
-      </c>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B36" s="12"/>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B37" s="36"/>
+      <c r="C26" s="6">
+        <v>2.3E-3</v>
+      </c>
+      <c r="E26" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="5">
+        <f>AVERAGE(I10:J10)</f>
+        <v>3.9855382206779161E-4</v>
+      </c>
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>117</v>
+      </c>
+      <c r="C28" s="6">
+        <f>AVERAGE(0.42%,1.05%)*2.5%</f>
+        <v>1.8375000000000002E-4</v>
+      </c>
+      <c r="E28" s="4"/>
+    </row>
+    <row r="29" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>118</v>
+      </c>
+      <c r="C29" s="5">
+        <v>0</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+    </row>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>119</v>
+      </c>
+      <c r="C30" s="5">
+        <f>SUM(C26:C29)</f>
+        <v>2.8823038220677916E-3</v>
+      </c>
+      <c r="D30" s="4">
+        <f>'Tracking Difference'!O39/100</f>
+        <v>3.3399999999999997E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="E31" s="4"/>
+    </row>
+    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>127</v>
+      </c>
+      <c r="E32" s="4"/>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="12"/>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="36"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3041,7 +3239,7 @@
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
@@ -3055,10 +3253,10 @@
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.25">
@@ -3097,7 +3295,7 @@
       </c>
       <c r="G5" s="2"/>
       <c r="J5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
@@ -3147,19 +3345,19 @@
         <v>16</v>
       </c>
       <c r="C8" s="4">
-        <f>'Northern Trust Master fondsen'!D54</f>
+        <f>'Northern Trust Master fondsen'!D44</f>
         <v>1.4240200701548999E-4</v>
       </c>
       <c r="D8" s="4">
-        <f>'Northern Trust Master fondsen'!E54</f>
+        <f>'Northern Trust Master fondsen'!E44</f>
         <v>1.8879294676940906E-4</v>
       </c>
       <c r="E8" s="4">
-        <f>'Northern Trust Master fondsen'!F54</f>
+        <f>'Northern Trust Master fondsen'!F44</f>
         <v>5.4497376783190948E-5</v>
       </c>
       <c r="F8" s="4">
-        <f>'Northern Trust Master fondsen'!G54</f>
+        <f>'Northern Trust Master fondsen'!G44</f>
         <v>4.2326604352244424E-5</v>
       </c>
       <c r="G8" s="4"/>
@@ -3193,7 +3391,7 @@
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C10" s="3">
         <v>1.4E-3</v>
@@ -3223,7 +3421,7 @@
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C12" s="15">
         <f>49806-C5</f>
@@ -3247,7 +3445,7 @@
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C13" s="3">
         <f>C12/C6</f>
@@ -3280,7 +3478,7 @@
     </row>
     <row r="15" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C15" s="24">
         <f>0.03</f>
@@ -3310,7 +3508,7 @@
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C17" s="6">
         <f>H9+H13</f>
@@ -3326,10 +3524,10 @@
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C18" s="3">
-        <f>'Tracking Difference'!O22/100</f>
+        <f>'Tracking Difference'!O24/100</f>
         <v>3.274999999999998E-3</v>
       </c>
       <c r="D18" s="4" t="s">
@@ -3391,7 +3589,7 @@
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C23" s="25">
         <f>C21-C17</f>
@@ -3462,7 +3660,7 @@
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
@@ -3476,10 +3674,10 @@
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.25">
@@ -3518,7 +3716,7 @@
       </c>
       <c r="G5" s="2"/>
       <c r="J5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
@@ -3563,7 +3761,7 @@
       <c r="H7" s="5"/>
       <c r="I7" s="3"/>
       <c r="J7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3571,19 +3769,19 @@
         <v>16</v>
       </c>
       <c r="C8" s="3">
-        <f>'Northern Trust Master fondsen'!D41</f>
+        <f>'Northern Trust Master fondsen'!D31</f>
         <v>4.0880326741039955E-4</v>
       </c>
       <c r="D8" s="3">
-        <f>'Northern Trust Master fondsen'!E41</f>
+        <f>'Northern Trust Master fondsen'!E31</f>
         <v>3.2333263888189987E-4</v>
       </c>
       <c r="E8" s="3">
-        <f>'Northern Trust Master fondsen'!F41</f>
+        <f>'Northern Trust Master fondsen'!F31</f>
         <v>1.4029800153593462E-4</v>
       </c>
       <c r="F8" s="3">
-        <f>'Northern Trust Master fondsen'!G41</f>
+        <f>'Northern Trust Master fondsen'!G31</f>
         <v>1.0903789686451616E-4</v>
       </c>
       <c r="G8" s="4"/>
@@ -3617,7 +3815,7 @@
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C10" s="3">
         <v>6.9999999999999999E-4</v>
@@ -3647,7 +3845,7 @@
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C12" s="15">
         <f>73959-C5</f>
@@ -3671,7 +3869,7 @@
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C13" s="3">
         <f>C12/C6</f>
@@ -3705,7 +3903,7 @@
     </row>
     <row r="15" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C15" s="24">
         <f>0.03</f>
@@ -3735,7 +3933,7 @@
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C17" s="6">
         <f>H9+H13</f>
@@ -3751,10 +3949,10 @@
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C18" s="3">
-        <f>'Tracking Difference'!O30/100</f>
+        <f>'Tracking Difference'!O32/100</f>
         <v>1.6499999999999959E-3</v>
       </c>
       <c r="D18" s="4" t="s">
@@ -3816,7 +4014,7 @@
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C23" s="25">
         <f>C21-C17</f>
@@ -3916,16 +4114,16 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C245834D-4F6D-4A3C-9D7B-51919C891EFD}">
-  <dimension ref="B2:N64"/>
+  <dimension ref="B2:P54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="28.140625" customWidth="1"/>
     <col min="3" max="3" width="24.85546875" customWidth="1"/>
-    <col min="4" max="9" width="17.7109375" customWidth="1"/>
-    <col min="11" max="11" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="11" width="17.7109375" customWidth="1"/>
+    <col min="13" max="13" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B2" s="10" t="s">
         <v>10</v>
       </c>
@@ -3936,11 +4134,13 @@
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
-      <c r="K2" s="8" t="s">
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="M2" s="8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C3" s="1">
         <v>2015</v>
       </c>
@@ -3962,8 +4162,14 @@
       <c r="I3" s="1">
         <v>2021</v>
       </c>
-    </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="J3" s="1">
+        <v>2022</v>
+      </c>
+      <c r="K3" s="1">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
@@ -3986,11 +4192,17 @@
       <c r="I4" s="11">
         <v>168260</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="J4" s="11">
+        <v>192053</v>
+      </c>
+      <c r="K4" s="11">
+        <v>441244</v>
+      </c>
+      <c r="M4" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
@@ -4016,11 +4228,17 @@
       <c r="I5" s="11">
         <v>11268311752</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="J5" s="11">
+        <v>9250620202</v>
+      </c>
+      <c r="K5" s="11">
+        <v>11669111484</v>
+      </c>
+      <c r="M5" s="8" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
@@ -4049,750 +4267,724 @@
         <f>I4/AVERAGE(H5:I5)</f>
         <v>1.7136259660773064E-5</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="J6" s="4">
+        <f>J4/AVERAGE(I5:J5)</f>
+        <v>1.8719590320836442E-5</v>
+      </c>
+      <c r="K6" s="4">
+        <f>K4/AVERAGE(J5:K5)</f>
+        <v>4.2184479860732762E-5</v>
+      </c>
+      <c r="M6" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B7" s="1"/>
       <c r="C7" s="7"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
-      <c r="K7" s="8"/>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="M7" s="8"/>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B8" s="1"/>
       <c r="C8" s="7"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
-      <c r="F8" s="3">
-        <f>2849261/AVERAGE(F5:G5)</f>
-        <v>5.0310241219762278E-4</v>
-      </c>
-      <c r="G8" s="3">
-        <f>3430662/AVERAGE(F5:G5)</f>
-        <v>6.0576210029011761E-4</v>
-      </c>
-      <c r="K8" s="8"/>
-    </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B9" s="1"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="K9" s="8"/>
-    </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B10" s="1"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="K10" s="8" t="s">
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="M8" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B9" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" s="32">
+        <v>9156794</v>
+      </c>
+      <c r="D9" s="32">
+        <v>35680887</v>
+      </c>
+      <c r="E9" s="32">
+        <v>59639049</v>
+      </c>
+      <c r="F9" s="32">
+        <v>98224310</v>
+      </c>
+      <c r="G9" s="32">
+        <v>140316975</v>
+      </c>
+      <c r="M9" s="8"/>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B10" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10" s="32">
+        <v>723455</v>
+      </c>
+      <c r="D10" s="32">
+        <v>3677107</v>
+      </c>
+      <c r="E10" s="32">
+        <v>6076660</v>
+      </c>
+      <c r="F10" s="32">
+        <v>10961948</v>
+      </c>
+      <c r="G10" s="32">
+        <v>14258476</v>
+      </c>
+      <c r="M10" s="13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C11" s="32">
-        <v>9156794</v>
-      </c>
-      <c r="D11" s="32">
-        <v>35680887</v>
-      </c>
-      <c r="E11" s="32">
-        <v>59639049</v>
-      </c>
-      <c r="F11" s="32">
-        <v>98224310</v>
-      </c>
-      <c r="G11" s="32">
-        <v>140316975</v>
-      </c>
-      <c r="K11" s="8"/>
-    </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B12" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" s="32">
-        <v>723455</v>
-      </c>
-      <c r="D12" s="32">
-        <v>3677107</v>
-      </c>
-      <c r="E12" s="32">
-        <v>6076660</v>
-      </c>
-      <c r="F12" s="32">
-        <v>10961948</v>
-      </c>
-      <c r="G12" s="32">
-        <v>14258476</v>
-      </c>
-      <c r="K12" s="13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B13" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C13" s="23">
-        <f t="shared" ref="C13:F13" si="1">C12/C11</f>
+      <c r="C11" s="23">
+        <f t="shared" ref="C11:F11" si="1">C10/C9</f>
         <v>7.9007456103085863E-2</v>
       </c>
-      <c r="D13" s="23">
+      <c r="D11" s="23">
         <f t="shared" si="1"/>
         <v>0.10305536967172368</v>
       </c>
-      <c r="E13" s="23">
+      <c r="E11" s="23">
         <f t="shared" si="1"/>
         <v>0.10189062538539137</v>
       </c>
-      <c r="F13" s="23">
+      <c r="F11" s="23">
         <f t="shared" si="1"/>
         <v>0.11160117083031686</v>
       </c>
-      <c r="G13" s="23">
-        <f>G12/G11</f>
+      <c r="G11" s="23">
+        <f>G10/G9</f>
         <v>0.10161618720757057</v>
       </c>
-      <c r="K13" s="8" t="s">
+      <c r="M11" s="8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B14" s="1"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="34"/>
-    </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B15" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C15" s="3">
-        <v>1E-4</v>
-      </c>
-      <c r="D15" s="3">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B12" s="1"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="34"/>
+      <c r="J12" s="34"/>
+      <c r="K12" s="34"/>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B13" s="1"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="M13" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M14" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B16" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="10"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="M16" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C17" s="1">
+        <v>2015</v>
+      </c>
+      <c r="D17" s="1">
+        <v>2016</v>
+      </c>
+      <c r="E17" s="1">
+        <v>2017</v>
+      </c>
+      <c r="F17" s="1">
+        <v>2018</v>
+      </c>
+      <c r="G17" s="1">
+        <v>2019</v>
+      </c>
+      <c r="H17" s="1">
+        <v>2020</v>
+      </c>
+      <c r="I17" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J17" s="1">
+        <v>2022</v>
+      </c>
+      <c r="K17" s="1">
+        <v>2023</v>
+      </c>
+      <c r="M17" t="s">
+        <v>106</v>
+      </c>
+      <c r="N17" s="5"/>
+      <c r="P17" s="5"/>
+    </row>
+    <row r="18" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2">
+        <v>63179</v>
+      </c>
+      <c r="H18" s="2">
+        <v>78222</v>
+      </c>
+      <c r="I18" s="2">
+        <v>88354</v>
+      </c>
+      <c r="J18" s="2">
+        <v>154570</v>
+      </c>
+      <c r="K18" s="2">
+        <v>127992</v>
+      </c>
+      <c r="M18" t="s">
+        <v>92</v>
+      </c>
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2">
         <v>0</v>
       </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="G15" s="3">
-        <v>1E-4</v>
-      </c>
-      <c r="K15" s="8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="K16" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B18" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="K18" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C19" s="1">
-        <v>2015</v>
-      </c>
-      <c r="D19" s="1">
-        <v>2016</v>
-      </c>
-      <c r="E19" s="1">
-        <v>2017</v>
-      </c>
-      <c r="F19" s="1">
-        <v>2018</v>
-      </c>
-      <c r="G19" s="1">
-        <v>2019</v>
-      </c>
-      <c r="H19" s="1">
-        <v>2020</v>
-      </c>
-      <c r="I19" s="1">
-        <v>2021</v>
-      </c>
-      <c r="K19" t="s">
-        <v>117</v>
-      </c>
-      <c r="L19" s="5"/>
-      <c r="N19" s="5"/>
-    </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="G19" s="2">
+        <v>141467154</v>
+      </c>
+      <c r="H19" s="2">
+        <v>333543399</v>
+      </c>
+      <c r="I19" s="2">
+        <v>798324455</v>
+      </c>
+      <c r="J19" s="2">
+        <v>1079744168</v>
+      </c>
+      <c r="K19" s="2">
+        <v>1473612604</v>
+      </c>
+      <c r="P19" s="5"/>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2">
-        <v>63179</v>
-      </c>
-      <c r="H20" s="2">
-        <v>78222</v>
-      </c>
-      <c r="I20" s="2">
-        <v>88354</v>
-      </c>
-      <c r="K20" t="s">
-        <v>94</v>
-      </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B21" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2">
-        <v>0</v>
-      </c>
-      <c r="G21" s="2">
-        <v>141467154</v>
-      </c>
-      <c r="H21" s="2">
-        <v>333543399</v>
-      </c>
-      <c r="I21" s="2">
-        <v>798324455</v>
-      </c>
-      <c r="N21" s="5"/>
-    </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="31">
+        <f>G18/AVERAGE(F19:G19)</f>
+        <v>8.9319673455790307E-4</v>
+      </c>
+      <c r="H20" s="31">
+        <f>H18/AVERAGE(G19:H19)</f>
+        <v>3.2934847239067549E-4</v>
+      </c>
+      <c r="I20" s="31">
+        <f>I18/AVERAGE(H19:I19)</f>
+        <v>1.5612069852104837E-4</v>
+      </c>
+      <c r="J20" s="31">
+        <f>J18/AVERAGE(I19:J19)</f>
+        <v>1.6460527385106098E-4</v>
+      </c>
+      <c r="K20" s="31">
+        <f>K18/AVERAGE(J19:K19)</f>
+        <v>1.0025390999295887E-4</v>
+      </c>
+    </row>
+    <row r="21" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B21" s="1"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="31"/>
+    </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="31">
-        <f>G20/AVERAGE(F21:G21)</f>
-        <v>8.9319673455790307E-4</v>
-      </c>
-      <c r="H22" s="31">
-        <f>H20/AVERAGE(G21:H21)</f>
-        <v>3.2934847239067549E-4</v>
-      </c>
-      <c r="I22" s="31">
-        <f>I20/AVERAGE(H21:I21)</f>
-        <v>1.5612069852104837E-4</v>
-      </c>
-    </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B23" s="1"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="31"/>
-    </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="33">
+        <v>1485197</v>
+      </c>
+    </row>
+    <row r="23" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B23" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="33"/>
+      <c r="F23" s="33"/>
+      <c r="G23" s="33">
+        <v>195155</v>
+      </c>
+      <c r="M23" s="8"/>
+    </row>
+    <row r="24" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C24" s="32"/>
-      <c r="D24" s="32"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="33">
-        <v>1485197</v>
-      </c>
-    </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B25" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C25" s="32"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="33">
-        <v>195155</v>
-      </c>
-      <c r="K25" s="8"/>
-    </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B26" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="30">
-        <f>G25/G24</f>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30">
+        <f>G23/G22</f>
         <v>0.13140007689215638</v>
       </c>
-      <c r="K26" s="8"/>
-    </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B27" s="1"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="31"/>
-    </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="M24" s="8"/>
+    </row>
+    <row r="25" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B25" s="1"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="31"/>
+    </row>
+    <row r="26" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B26" s="1"/>
+    </row>
+    <row r="27" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B27" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" s="10"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+    </row>
+    <row r="28" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="G28" s="3">
-        <v>1E-4</v>
-      </c>
-    </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B29" s="1"/>
-      <c r="G29" s="3"/>
-    </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B30" s="1"/>
-      <c r="G30" s="3"/>
-    </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B31" s="1"/>
-      <c r="G31" s="3"/>
-    </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="C28" s="1">
+        <v>2015</v>
+      </c>
+      <c r="D28" s="1">
+        <v>2016</v>
+      </c>
+      <c r="E28" s="1">
+        <v>2017</v>
+      </c>
+      <c r="F28" s="1">
+        <v>2018</v>
+      </c>
+      <c r="G28" s="1">
+        <v>2019</v>
+      </c>
+      <c r="H28" s="1">
+        <v>2020</v>
+      </c>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="N28" s="6"/>
+    </row>
+    <row r="29" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2">
+        <v>45547</v>
+      </c>
+      <c r="E29" s="2">
+        <v>119882</v>
+      </c>
+      <c r="F29" s="2">
+        <v>97972</v>
+      </c>
+      <c r="G29" s="2">
+        <v>119750</v>
+      </c>
+      <c r="M29" s="8"/>
+      <c r="N29" s="6"/>
+    </row>
+    <row r="30" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B30" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="2">
+        <v>25275750</v>
+      </c>
+      <c r="D30" s="2">
+        <v>197555150</v>
+      </c>
+      <c r="E30" s="2">
+        <v>543984587</v>
+      </c>
+      <c r="F30" s="2">
+        <v>852642577</v>
+      </c>
+      <c r="G30" s="2">
+        <v>1343841461</v>
+      </c>
+    </row>
+    <row r="31" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="7"/>
+      <c r="D31" s="4">
+        <f t="shared" ref="D31" si="2">D29/AVERAGE(C30:D30)</f>
+        <v>4.0880326741039955E-4</v>
+      </c>
+      <c r="E31" s="4">
+        <f t="shared" ref="E31" si="3">E29/AVERAGE(D30:E30)</f>
+        <v>3.2333263888189987E-4</v>
+      </c>
+      <c r="F31" s="4">
+        <f t="shared" ref="F31" si="4">F29/AVERAGE(E30:F30)</f>
+        <v>1.4029800153593462E-4</v>
+      </c>
+      <c r="G31" s="4">
+        <f>G29/AVERAGE(F30:G30)</f>
+        <v>1.0903789686451616E-4</v>
+      </c>
+    </row>
+    <row r="32" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B32" s="1"/>
-      <c r="G32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B33" s="1"/>
-      <c r="G33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B34" s="1"/>
-      <c r="G34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B35" s="1"/>
-      <c r="G35" s="3"/>
-    </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B36" s="1"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B37" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C37" s="10"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="9"/>
-    </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B38" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C38" s="1">
-        <v>2015</v>
-      </c>
-      <c r="D38" s="1">
-        <v>2016</v>
-      </c>
-      <c r="E38" s="1">
-        <v>2017</v>
-      </c>
-      <c r="F38" s="1">
-        <v>2018</v>
-      </c>
-      <c r="G38" s="1">
-        <v>2019</v>
-      </c>
-      <c r="H38" s="1">
-        <v>2020</v>
-      </c>
-      <c r="I38" s="1"/>
-      <c r="L38" s="6"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B39" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2">
-        <v>45547</v>
-      </c>
-      <c r="E39" s="2">
-        <v>119882</v>
-      </c>
-      <c r="F39" s="2">
-        <v>97972</v>
-      </c>
-      <c r="G39" s="2">
-        <v>119750</v>
-      </c>
-      <c r="K39" s="8"/>
-      <c r="L39" s="6"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B40" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C40" s="2">
-        <v>25275750</v>
-      </c>
-      <c r="D40" s="2">
-        <v>197555150</v>
-      </c>
-      <c r="E40" s="2">
-        <v>543984587</v>
-      </c>
-      <c r="F40" s="2">
-        <v>852642577</v>
-      </c>
-      <c r="G40" s="2">
-        <v>1343841461</v>
-      </c>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B41" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C41" s="7"/>
-      <c r="D41" s="4">
-        <f t="shared" ref="D41" si="2">D39/AVERAGE(C40:D40)</f>
-        <v>4.0880326741039955E-4</v>
-      </c>
-      <c r="E41" s="4">
-        <f t="shared" ref="E41" si="3">E39/AVERAGE(D40:E40)</f>
-        <v>3.2333263888189987E-4</v>
-      </c>
-      <c r="F41" s="4">
-        <f t="shared" ref="F41" si="4">F39/AVERAGE(E40:F40)</f>
-        <v>1.4029800153593462E-4</v>
-      </c>
-      <c r="G41" s="4">
-        <f>G39/AVERAGE(F40:G40)</f>
-        <v>1.0903789686451616E-4</v>
-      </c>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B42" s="1"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B43" s="1" t="s">
+      <c r="C32" s="7"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B33" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C33" s="32">
+        <v>4178257</v>
+      </c>
+      <c r="D33" s="32">
+        <v>4523050</v>
+      </c>
+      <c r="E33" s="32">
+        <v>11531574</v>
+      </c>
+      <c r="F33" s="32">
+        <v>25060715</v>
+      </c>
+      <c r="G33" s="32">
+        <v>36414801</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B34" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C34" s="32">
+        <v>460172</v>
+      </c>
+      <c r="D34" s="32">
+        <v>328239</v>
+      </c>
+      <c r="E34" s="32">
+        <v>769172</v>
+      </c>
+      <c r="F34" s="32">
+        <v>1404308</v>
+      </c>
+      <c r="G34" s="32">
+        <v>1974860</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B35" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C43" s="32">
-        <v>4178257</v>
-      </c>
-      <c r="D43" s="32">
-        <v>4523050</v>
-      </c>
-      <c r="E43" s="32">
-        <v>11531574</v>
-      </c>
-      <c r="F43" s="32">
-        <v>25060715</v>
-      </c>
-      <c r="G43" s="32">
-        <v>36414801</v>
-      </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B44" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C44" s="32">
-        <v>460172</v>
-      </c>
-      <c r="D44" s="32">
-        <v>328239</v>
-      </c>
-      <c r="E44" s="32">
-        <v>769172</v>
-      </c>
-      <c r="F44" s="32">
-        <v>1404308</v>
-      </c>
-      <c r="G44" s="32">
-        <v>1974860</v>
-      </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B45" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C45" s="23">
-        <f t="shared" ref="C45:F45" si="5">C44/C43</f>
+      <c r="C35" s="23">
+        <f t="shared" ref="C35:F35" si="5">C34/C33</f>
         <v>0.11013491989602363</v>
       </c>
-      <c r="D45" s="23">
+      <c r="D35" s="23">
         <f t="shared" si="5"/>
         <v>7.2570278904721369E-2</v>
       </c>
-      <c r="E45" s="23">
+      <c r="E35" s="23">
         <f t="shared" si="5"/>
         <v>6.6701388726291833E-2</v>
       </c>
-      <c r="F45" s="23">
+      <c r="F35" s="23">
         <f t="shared" si="5"/>
         <v>5.603623041082427E-2</v>
       </c>
-      <c r="G45" s="23">
-        <f>G44/G43</f>
+      <c r="G35" s="23">
+        <f>G34/G33</f>
         <v>5.4232343601163711E-2</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B46" s="1"/>
-      <c r="C46" s="23"/>
-      <c r="D46" s="23"/>
-      <c r="E46" s="23"/>
-      <c r="F46" s="23"/>
-      <c r="G46" s="23"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B36" s="1"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="23"/>
+      <c r="G36" s="23"/>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B37" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C37" s="3">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="D37" s="3">
+        <v>1E-4</v>
+      </c>
+      <c r="E37" s="3">
+        <v>0</v>
+      </c>
+      <c r="F37" s="3">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="G37" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B38" s="1"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+    </row>
+    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B40" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C40" s="10"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="9"/>
+      <c r="K40" s="9"/>
+    </row>
+    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B41" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C41" s="1">
+        <v>2015</v>
+      </c>
+      <c r="D41" s="1">
+        <v>2016</v>
+      </c>
+      <c r="E41" s="1">
+        <v>2017</v>
+      </c>
+      <c r="F41" s="1">
+        <v>2018</v>
+      </c>
+      <c r="G41" s="1">
+        <v>2019</v>
+      </c>
+      <c r="H41" s="1">
+        <v>2020</v>
+      </c>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+    </row>
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B42" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2">
+        <v>10837</v>
+      </c>
+      <c r="E42" s="2">
+        <v>77254</v>
+      </c>
+      <c r="F42" s="2">
+        <v>45684</v>
+      </c>
+      <c r="G42" s="2">
+        <v>55573</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B43" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43" s="2">
+        <v>82931512</v>
+      </c>
+      <c r="D43" s="2">
+        <v>69271399</v>
+      </c>
+      <c r="E43" s="2">
+        <v>749127819</v>
+      </c>
+      <c r="F43" s="2">
+        <v>927429942</v>
+      </c>
+      <c r="G43" s="2">
+        <v>1698483516</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B44" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="7"/>
+      <c r="D44" s="4">
+        <f t="shared" ref="D44" si="6">D42/AVERAGE(C43:D43)</f>
+        <v>1.4240200701548999E-4</v>
+      </c>
+      <c r="E44" s="4">
+        <f t="shared" ref="E44" si="7">E42/AVERAGE(D43:E43)</f>
+        <v>1.8879294676940906E-4</v>
+      </c>
+      <c r="F44" s="4">
+        <f t="shared" ref="F44" si="8">F42/AVERAGE(E43:F43)</f>
+        <v>5.4497376783190948E-5</v>
+      </c>
+      <c r="G44" s="4">
+        <f>G42/AVERAGE(F43:G43)</f>
+        <v>4.2326604352244424E-5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B46" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C46" s="32">
+        <v>13588</v>
+      </c>
+      <c r="D46" s="32">
+        <v>812657</v>
+      </c>
+      <c r="E46" s="32">
+        <v>9763753</v>
+      </c>
+      <c r="F46" s="32">
+        <v>18127165</v>
+      </c>
+      <c r="G46" s="32">
+        <v>28988001</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B47" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C47" s="3">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="D47" s="3">
-        <v>1E-4</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>2.0000000000000001E-4</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B48" s="1"/>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3"/>
-      <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
-    </row>
-    <row r="50" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B50" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C50" s="10"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="9"/>
-      <c r="H50" s="9"/>
-      <c r="I50" s="9"/>
-    </row>
-    <row r="51" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B51" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C51" s="1">
-        <v>2015</v>
-      </c>
-      <c r="D51" s="1">
-        <v>2016</v>
-      </c>
-      <c r="E51" s="1">
-        <v>2017</v>
-      </c>
-      <c r="F51" s="1">
-        <v>2018</v>
-      </c>
-      <c r="G51" s="1">
-        <v>2019</v>
-      </c>
-      <c r="H51" s="1">
-        <v>2020</v>
-      </c>
-      <c r="I51" s="1"/>
-    </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B52" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2">
-        <v>10837</v>
-      </c>
-      <c r="E52" s="2">
-        <v>77254</v>
-      </c>
-      <c r="F52" s="2">
-        <v>45684</v>
-      </c>
-      <c r="G52" s="2">
-        <v>55573</v>
-      </c>
-    </row>
-    <row r="53" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B53" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C53" s="2">
-        <v>82931512</v>
-      </c>
-      <c r="D53" s="2">
-        <v>69271399</v>
-      </c>
-      <c r="E53" s="2">
-        <v>749127819</v>
-      </c>
-      <c r="F53" s="2">
-        <v>927429942</v>
-      </c>
-      <c r="G53" s="2">
-        <v>1698483516</v>
-      </c>
-    </row>
-    <row r="54" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B54" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="4">
-        <f t="shared" ref="D54" si="6">D52/AVERAGE(C53:D53)</f>
-        <v>1.4240200701548999E-4</v>
-      </c>
-      <c r="E54" s="4">
-        <f t="shared" ref="E54" si="7">E52/AVERAGE(D53:E53)</f>
-        <v>1.8879294676940906E-4</v>
-      </c>
-      <c r="F54" s="4">
-        <f t="shared" ref="F54" si="8">F52/AVERAGE(E53:F53)</f>
-        <v>5.4497376783190948E-5</v>
-      </c>
-      <c r="G54" s="4">
-        <f>G52/AVERAGE(F53:G53)</f>
-        <v>4.2326604352244424E-5</v>
-      </c>
-    </row>
-    <row r="56" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B56" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C47" s="32">
+        <v>1921</v>
+      </c>
+      <c r="D47" s="32">
+        <v>121637</v>
+      </c>
+      <c r="E47" s="32">
+        <v>1181144</v>
+      </c>
+      <c r="F47" s="32">
+        <v>2300880</v>
+      </c>
+      <c r="G47" s="32">
+        <v>3641394</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B48" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C56" s="32">
-        <v>13588</v>
-      </c>
-      <c r="D56" s="32">
-        <v>812657</v>
-      </c>
-      <c r="E56" s="32">
-        <v>9763753</v>
-      </c>
-      <c r="F56" s="32">
-        <v>18127165</v>
-      </c>
-      <c r="G56" s="32">
-        <v>28988001</v>
-      </c>
-    </row>
-    <row r="57" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B57" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C57" s="32">
-        <v>1921</v>
-      </c>
-      <c r="D57" s="32">
-        <v>121637</v>
-      </c>
-      <c r="E57" s="32">
-        <v>1181144</v>
-      </c>
-      <c r="F57" s="32">
-        <v>2300880</v>
-      </c>
-      <c r="G57" s="32">
-        <v>3641394</v>
-      </c>
-    </row>
-    <row r="58" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B58" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C58" s="23">
-        <f t="shared" ref="C58:F58" si="9">C57/C56</f>
+      <c r="C48" s="23">
+        <f t="shared" ref="C48:F48" si="9">C47/C46</f>
         <v>0.14137474241978215</v>
       </c>
-      <c r="D58" s="23">
+      <c r="D48" s="23">
         <f t="shared" si="9"/>
         <v>0.1496781544981462</v>
       </c>
-      <c r="E58" s="23">
+      <c r="E48" s="23">
         <f t="shared" si="9"/>
         <v>0.12097233512564277</v>
       </c>
-      <c r="F58" s="23">
+      <c r="F48" s="23">
         <f t="shared" si="9"/>
         <v>0.12692994188556236</v>
       </c>
-      <c r="G58" s="23">
-        <f>G57/G56</f>
+      <c r="G48" s="23">
+        <f>G47/G46</f>
         <v>0.1256172855796438</v>
       </c>
     </row>
-    <row r="60" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B60" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C60" s="3">
+    <row r="50" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B50" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C50" s="3">
         <v>0</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D50" s="3">
         <v>0</v>
       </c>
-      <c r="E60" s="3">
+      <c r="E50" s="3">
         <v>0</v>
       </c>
-      <c r="F60" s="3">
+      <c r="F50" s="3">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="G60" s="3">
+      <c r="G50" s="3">
         <v>1E-4</v>
       </c>
     </row>
-    <row r="64" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="E64" s="3"/>
+    <row r="54" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="E54" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4803,7 +4995,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F528616F-4365-4E03-AA99-F5C2282C78C2}">
-  <dimension ref="B2:AJ63"/>
+  <dimension ref="B2:AJ65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="73" bestFit="1" customWidth="1"/>
@@ -4853,12 +5045,12 @@
         <v>42</v>
       </c>
       <c r="S2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B3" s="18" t="s">
-        <v>61</v>
+        <v>120</v>
       </c>
       <c r="C3" s="19"/>
       <c r="D3" s="19"/>
@@ -4893,7 +5085,7 @@
       <c r="O3" s="16"/>
       <c r="P3" s="19"/>
       <c r="S3" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="2:36" x14ac:dyDescent="0.25">
@@ -4937,7 +5129,7 @@
       <c r="O4" s="16"/>
       <c r="P4" s="16"/>
       <c r="S4" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="2:36" x14ac:dyDescent="0.25">
@@ -5075,110 +5267,46 @@
       </c>
       <c r="P7" s="19"/>
     </row>
-    <row r="10" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B10" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22">
-        <v>12.94</v>
-      </c>
-      <c r="F10" s="22">
-        <v>21.63</v>
-      </c>
-      <c r="G10" s="22">
-        <v>-10.75</v>
-      </c>
-      <c r="H10" s="22">
-        <v>20.82</v>
-      </c>
-      <c r="I10" s="22">
-        <v>10.26</v>
-      </c>
-      <c r="J10" s="22">
-        <v>3.81</v>
-      </c>
-      <c r="K10" s="22">
-        <v>-15.57</v>
-      </c>
-      <c r="L10" s="22">
-        <v>5.57</v>
-      </c>
-      <c r="M10" s="22">
-        <v>15.02</v>
-      </c>
-      <c r="N10" s="22"/>
-      <c r="O10" s="20"/>
-      <c r="P10" s="22"/>
-    </row>
-    <row r="11" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B11" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" s="22">
-        <v>12.03</v>
-      </c>
-      <c r="D11" s="22">
-        <v>-3.64</v>
-      </c>
-      <c r="E11" s="22">
-        <v>13.57</v>
-      </c>
-      <c r="F11" s="22">
-        <v>21.71</v>
-      </c>
-      <c r="G11" s="22">
-        <v>-10.25</v>
-      </c>
-      <c r="H11" s="22">
-        <v>21.08</v>
-      </c>
-      <c r="I11" s="22">
-        <v>10.72</v>
-      </c>
-      <c r="J11" s="22">
-        <v>4.07</v>
-      </c>
-      <c r="K11" s="22"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="22"/>
-      <c r="N11" s="22"/>
-      <c r="O11" s="20"/>
-      <c r="P11" s="22"/>
+    <row r="9" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B9" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="M9">
+        <v>26.57</v>
+      </c>
     </row>
     <row r="12" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B12" s="21" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="C12" s="22"/>
       <c r="D12" s="22"/>
       <c r="E12" s="22">
-        <v>13.14</v>
+        <v>12.94</v>
       </c>
       <c r="F12" s="22">
-        <v>21.3</v>
+        <v>21.63</v>
       </c>
       <c r="G12" s="22">
-        <v>-10.6</v>
+        <v>-10.75</v>
       </c>
       <c r="H12" s="22">
-        <v>20.61</v>
+        <v>20.82</v>
       </c>
       <c r="I12" s="22">
-        <v>10.37</v>
+        <v>10.26</v>
       </c>
       <c r="J12" s="22">
-        <v>3.74</v>
+        <v>3.81</v>
       </c>
       <c r="K12" s="22">
-        <v>-15.59</v>
+        <v>-15.57</v>
       </c>
       <c r="L12" s="22">
-        <v>5.89</v>
+        <v>5.57</v>
       </c>
       <c r="M12" s="22">
-        <v>14.95</v>
+        <v>15.02</v>
       </c>
       <c r="N12" s="22"/>
       <c r="O12" s="20"/>
@@ -5186,794 +5314,935 @@
     </row>
     <row r="13" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B13" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
+        <v>43</v>
+      </c>
+      <c r="C13" s="22">
+        <v>12.03</v>
+      </c>
+      <c r="D13" s="22">
+        <v>-3.64</v>
+      </c>
       <c r="E13" s="22">
-        <f t="shared" ref="E13:M13" si="2">E10-E12</f>
-        <v>-0.20000000000000107</v>
+        <v>13.57</v>
       </c>
       <c r="F13" s="22">
-        <f t="shared" si="2"/>
-        <v>0.32999999999999829</v>
+        <v>21.71</v>
       </c>
       <c r="G13" s="22">
-        <f t="shared" si="2"/>
-        <v>-0.15000000000000036</v>
+        <v>-10.25</v>
       </c>
       <c r="H13" s="22">
-        <f t="shared" si="2"/>
-        <v>0.21000000000000085</v>
+        <v>21.08</v>
       </c>
       <c r="I13" s="22">
-        <f t="shared" si="2"/>
-        <v>-0.10999999999999943</v>
+        <v>10.72</v>
       </c>
       <c r="J13" s="22">
-        <f t="shared" si="2"/>
-        <v>6.999999999999984E-2</v>
+        <v>4.07</v>
       </c>
       <c r="K13" s="22">
-        <f t="shared" si="2"/>
-        <v>1.9999999999999574E-2</v>
+        <v>-15.23</v>
       </c>
       <c r="L13" s="22">
-        <f t="shared" si="2"/>
-        <v>-0.3199999999999994</v>
+        <v>6.3</v>
       </c>
       <c r="M13" s="22">
-        <f t="shared" si="2"/>
-        <v>7.0000000000000284E-2</v>
+        <v>15.54</v>
       </c>
       <c r="N13" s="22"/>
-      <c r="O13" s="22"/>
-      <c r="P13" s="22">
-        <f>AVERAGE(E13:M13)</f>
-        <v>-8.888888888889045E-3</v>
-      </c>
-      <c r="AB13" s="1">
-        <f t="shared" ref="AB13:AD13" si="3">E2</f>
-        <v>2016</v>
-      </c>
-      <c r="AC13" s="1">
-        <f t="shared" si="3"/>
-        <v>2017</v>
-      </c>
-      <c r="AD13" s="1">
-        <f t="shared" si="3"/>
-        <v>2018</v>
-      </c>
-      <c r="AE13" s="1">
-        <f t="shared" ref="AE13:AJ14" si="4">H2</f>
-        <v>2019</v>
-      </c>
-      <c r="AF13" s="1">
-        <f t="shared" si="4"/>
-        <v>2020</v>
-      </c>
-      <c r="AG13" s="1">
-        <f t="shared" si="4"/>
-        <v>2021</v>
-      </c>
-      <c r="AH13" s="1">
-        <f t="shared" si="4"/>
-        <v>2022</v>
-      </c>
-      <c r="AI13" s="1">
-        <f t="shared" si="4"/>
-        <v>2023</v>
-      </c>
-      <c r="AJ13" s="1">
-        <f t="shared" si="4"/>
-        <v>2024</v>
-      </c>
+      <c r="O13" s="20"/>
+      <c r="P13" s="22"/>
     </row>
     <row r="14" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B14" s="21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" s="22"/>
       <c r="D14" s="22"/>
       <c r="E14" s="22">
-        <f t="shared" ref="E14:J14" si="5">E11-E10</f>
+        <v>13.14</v>
+      </c>
+      <c r="F14" s="22">
+        <v>21.3</v>
+      </c>
+      <c r="G14" s="22">
+        <v>-10.6</v>
+      </c>
+      <c r="H14" s="22">
+        <v>20.61</v>
+      </c>
+      <c r="I14" s="22">
+        <v>10.37</v>
+      </c>
+      <c r="J14" s="22">
+        <v>3.74</v>
+      </c>
+      <c r="K14" s="22">
+        <v>-15.59</v>
+      </c>
+      <c r="L14" s="22">
+        <v>5.89</v>
+      </c>
+      <c r="M14" s="22">
+        <v>14.95</v>
+      </c>
+      <c r="N14" s="22"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="22"/>
+    </row>
+    <row r="15" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B15" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22">
+        <f t="shared" ref="E15:M15" si="2">E12-E14</f>
+        <v>-0.20000000000000107</v>
+      </c>
+      <c r="F15" s="22">
+        <f t="shared" si="2"/>
+        <v>0.32999999999999829</v>
+      </c>
+      <c r="G15" s="22">
+        <f t="shared" si="2"/>
+        <v>-0.15000000000000036</v>
+      </c>
+      <c r="H15" s="22">
+        <f t="shared" si="2"/>
+        <v>0.21000000000000085</v>
+      </c>
+      <c r="I15" s="22">
+        <f t="shared" si="2"/>
+        <v>-0.10999999999999943</v>
+      </c>
+      <c r="J15" s="22">
+        <f t="shared" si="2"/>
+        <v>6.999999999999984E-2</v>
+      </c>
+      <c r="K15" s="22">
+        <f t="shared" si="2"/>
+        <v>1.9999999999999574E-2</v>
+      </c>
+      <c r="L15" s="22">
+        <f t="shared" si="2"/>
+        <v>-0.3199999999999994</v>
+      </c>
+      <c r="M15" s="22">
+        <f t="shared" si="2"/>
+        <v>7.0000000000000284E-2</v>
+      </c>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22"/>
+      <c r="P15" s="22">
+        <f>AVERAGE(E15:M15)</f>
+        <v>-8.888888888889045E-3</v>
+      </c>
+      <c r="AB15" s="1">
+        <f t="shared" ref="AB15:AD15" si="3">E2</f>
+        <v>2016</v>
+      </c>
+      <c r="AC15" s="1">
+        <f t="shared" si="3"/>
+        <v>2017</v>
+      </c>
+      <c r="AD15" s="1">
+        <f t="shared" si="3"/>
+        <v>2018</v>
+      </c>
+      <c r="AE15" s="1">
+        <f>H2</f>
+        <v>2019</v>
+      </c>
+      <c r="AF15" s="1">
+        <f>I2</f>
+        <v>2020</v>
+      </c>
+      <c r="AG15" s="1">
+        <f>J2</f>
+        <v>2021</v>
+      </c>
+      <c r="AH15" s="1">
+        <f>K2</f>
+        <v>2022</v>
+      </c>
+      <c r="AI15" s="1">
+        <f>L2</f>
+        <v>2023</v>
+      </c>
+      <c r="AJ15" s="1">
+        <f>M2</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="16" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B16" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22">
+        <f t="shared" ref="E16:M16" si="4">E13-E12</f>
         <v>0.63000000000000078</v>
       </c>
-      <c r="F14" s="22">
+      <c r="F16" s="22">
+        <f t="shared" si="4"/>
+        <v>8.0000000000001847E-2</v>
+      </c>
+      <c r="G16" s="22">
+        <f t="shared" si="4"/>
+        <v>0.5</v>
+      </c>
+      <c r="H16" s="22">
+        <f t="shared" si="4"/>
+        <v>0.25999999999999801</v>
+      </c>
+      <c r="I16" s="22">
+        <f t="shared" si="4"/>
+        <v>0.46000000000000085</v>
+      </c>
+      <c r="J16" s="22">
+        <f t="shared" si="4"/>
+        <v>0.26000000000000023</v>
+      </c>
+      <c r="K16" s="22">
+        <f t="shared" si="4"/>
+        <v>0.33999999999999986</v>
+      </c>
+      <c r="L16" s="22">
+        <f t="shared" si="4"/>
+        <v>0.72999999999999954</v>
+      </c>
+      <c r="M16" s="22">
+        <f t="shared" si="4"/>
+        <v>0.51999999999999957</v>
+      </c>
+      <c r="N16" s="22"/>
+      <c r="O16" s="27">
+        <f>AVERAGE(E16:M16)</f>
+        <v>0.4200000000000001</v>
+      </c>
+      <c r="P16" s="22"/>
+      <c r="AA16" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB16" s="26">
+        <f t="shared" ref="AB16:AD16" si="5">E3</f>
+        <v>10.55</v>
+      </c>
+      <c r="AC16" s="26">
         <f t="shared" si="5"/>
-        <v>8.0000000000001847E-2</v>
-      </c>
-      <c r="G14" s="22">
+        <v>8.32</v>
+      </c>
+      <c r="AD16" s="26">
         <f t="shared" si="5"/>
-        <v>0.5</v>
-      </c>
-      <c r="H14" s="22">
-        <f t="shared" si="5"/>
-        <v>0.25999999999999801</v>
-      </c>
-      <c r="I14" s="22">
-        <f t="shared" si="5"/>
-        <v>0.46000000000000085</v>
-      </c>
-      <c r="J14" s="22">
-        <f t="shared" si="5"/>
-        <v>0.26000000000000023</v>
-      </c>
-      <c r="K14" s="22"/>
-      <c r="L14" s="22"/>
-      <c r="M14" s="22"/>
-      <c r="N14" s="22"/>
-      <c r="O14" s="27">
-        <f>AVERAGE(E14:M14)</f>
-        <v>0.36500000000000027</v>
-      </c>
-      <c r="P14" s="22"/>
-      <c r="AA14" t="s">
-        <v>121</v>
-      </c>
-      <c r="AB14" s="26">
-        <f t="shared" ref="AB14:AD14" si="6">E3</f>
-        <v>10.55</v>
-      </c>
-      <c r="AC14" s="26">
+        <v>-3.3</v>
+      </c>
+      <c r="AE16" s="26">
+        <f>H3</f>
+        <v>30.93</v>
+      </c>
+      <c r="AF16" s="26">
+        <f>I3</f>
+        <v>8.2200000000000006</v>
+      </c>
+      <c r="AG16" s="26">
+        <f>J3</f>
+        <v>31.74</v>
+      </c>
+      <c r="AH16" s="26">
+        <f>K3</f>
+        <v>-13.71</v>
+      </c>
+      <c r="AI16" s="26">
+        <f>L3</f>
+        <v>20.51</v>
+      </c>
+      <c r="AJ16" s="26">
+        <f>M3</f>
+        <v>26.97</v>
+      </c>
+    </row>
+    <row r="18" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="AA18" t="s">
+        <v>111</v>
+      </c>
+      <c r="AB18" s="26">
+        <f t="shared" ref="AB18:AJ18" si="6">AB22-AB16</f>
+        <v>0.16999999999999993</v>
+      </c>
+      <c r="AC18" s="26">
         <f t="shared" si="6"/>
-        <v>8.32</v>
-      </c>
-      <c r="AD14" s="26">
+        <v>0.21999999999999886</v>
+      </c>
+      <c r="AD18" s="26">
         <f t="shared" si="6"/>
-        <v>-3.3</v>
-      </c>
-      <c r="AE14" s="26">
-        <f t="shared" si="4"/>
-        <v>30.93</v>
-      </c>
-      <c r="AF14" s="26">
-        <f t="shared" si="4"/>
-        <v>8.2200000000000006</v>
-      </c>
-      <c r="AG14" s="26">
-        <f t="shared" si="4"/>
-        <v>31.74</v>
-      </c>
-      <c r="AH14" s="26">
-        <f t="shared" si="4"/>
-        <v>-13.71</v>
-      </c>
-      <c r="AI14" s="26">
-        <f t="shared" si="4"/>
-        <v>20.51</v>
-      </c>
-      <c r="AJ14" s="26">
-        <f t="shared" si="4"/>
-        <v>26.97</v>
-      </c>
-    </row>
-    <row r="16" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="AA16" t="s">
-        <v>123</v>
-      </c>
-      <c r="AB16" s="26">
-        <f t="shared" ref="AB16:AJ16" si="7">AB20-AB14</f>
-        <v>0.16999999999999993</v>
-      </c>
-      <c r="AC16" s="26">
-        <f t="shared" si="7"/>
-        <v>0.21999999999999886</v>
-      </c>
-      <c r="AD16" s="26">
-        <f t="shared" si="7"/>
         <v>0.17999999999999972</v>
       </c>
-      <c r="AE16" s="26">
-        <f t="shared" si="7"/>
+      <c r="AE18" s="26">
+        <f t="shared" si="6"/>
         <v>0.24000000000000199</v>
       </c>
-      <c r="AF16" s="26">
-        <f t="shared" si="7"/>
+      <c r="AF18" s="26">
+        <f t="shared" si="6"/>
         <v>0.30999999999999872</v>
       </c>
-      <c r="AG16" s="26">
-        <f t="shared" si="7"/>
+      <c r="AG18" s="26">
+        <f t="shared" si="6"/>
         <v>0.25</v>
       </c>
-      <c r="AH16" s="26">
-        <f t="shared" si="7"/>
+      <c r="AH18" s="26">
+        <f t="shared" si="6"/>
         <v>0.12000000000000099</v>
       </c>
-      <c r="AI16" s="26">
-        <f t="shared" si="7"/>
+      <c r="AI18" s="26">
+        <f t="shared" si="6"/>
         <v>0.34999999999999787</v>
       </c>
-      <c r="AJ16" s="26">
-        <f t="shared" si="7"/>
+      <c r="AJ18" s="26">
+        <f t="shared" si="6"/>
         <v>0.42999999999999972</v>
-      </c>
-    </row>
-    <row r="17" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B17" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E17">
-        <v>14.75</v>
-      </c>
-      <c r="F17">
-        <v>7.07</v>
-      </c>
-      <c r="G17">
-        <v>0.35</v>
-      </c>
-      <c r="H17">
-        <v>34.049999999999997</v>
-      </c>
-      <c r="AA17" t="s">
-        <v>125</v>
-      </c>
-      <c r="AB17">
-        <v>0.03</v>
-      </c>
-      <c r="AC17">
-        <v>0.03</v>
-      </c>
-      <c r="AD17">
-        <v>0.12</v>
-      </c>
-      <c r="AE17">
-        <v>0.15</v>
-      </c>
-      <c r="AF17">
-        <v>0.15</v>
-      </c>
-      <c r="AG17">
-        <v>0.15</v>
-      </c>
-      <c r="AH17">
-        <v>0.15</v>
-      </c>
-      <c r="AI17">
-        <v>0.15</v>
-      </c>
-      <c r="AJ17">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="18" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B18" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="E18">
-        <v>14.47</v>
-      </c>
-      <c r="F18">
-        <v>6.77</v>
-      </c>
-      <c r="G18">
-        <v>0.02</v>
-      </c>
-      <c r="H18">
-        <v>33.590000000000003</v>
       </c>
     </row>
     <row r="19" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B19" s="21" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E19">
-        <v>15.19</v>
+        <v>14.75</v>
       </c>
       <c r="F19">
-        <v>7.39</v>
+        <v>7.07</v>
       </c>
       <c r="G19">
-        <v>0.57999999999999996</v>
+        <v>0.35</v>
       </c>
       <c r="H19">
-        <v>34.369999999999997</v>
+        <v>34.049999999999997</v>
       </c>
       <c r="AA19" t="s">
-        <v>124</v>
-      </c>
-      <c r="AB19" s="37">
-        <f>World!C17</f>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="AC19" s="37">
-        <f>World!D17</f>
-        <v>0.01</v>
-      </c>
-      <c r="AD19" s="37">
-        <f>World!E17</f>
-        <v>0.09</v>
-      </c>
-      <c r="AE19" s="37">
-        <f>World!F17</f>
-        <v>0.26</v>
-      </c>
-      <c r="AF19" s="37">
-        <f>World!G17</f>
-        <v>0.19</v>
-      </c>
-      <c r="AG19" s="37">
-        <f>World!H17</f>
-        <v>0.08</v>
-      </c>
-      <c r="AH19" s="37">
-        <f>World!I17</f>
-        <v>0.02</v>
-      </c>
-      <c r="AI19" s="37">
-        <f>World!J17</f>
-        <v>0.01</v>
-      </c>
-      <c r="AJ19" s="37">
-        <f>World!K17</f>
-        <v>0</v>
+        <v>113</v>
+      </c>
+      <c r="AB19">
+        <v>0.03</v>
+      </c>
+      <c r="AC19">
+        <v>0.03</v>
+      </c>
+      <c r="AD19">
+        <v>0.12</v>
+      </c>
+      <c r="AE19">
+        <v>0.15</v>
+      </c>
+      <c r="AF19">
+        <v>0.15</v>
+      </c>
+      <c r="AG19">
+        <v>0.15</v>
+      </c>
+      <c r="AH19">
+        <v>0.15</v>
+      </c>
+      <c r="AI19">
+        <v>0.15</v>
+      </c>
+      <c r="AJ19">
+        <v>0.15</v>
       </c>
     </row>
     <row r="20" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B20" s="21" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="E20">
-        <f>E19-E18</f>
-        <v>0.71999999999999886</v>
+        <v>14.47</v>
       </c>
       <c r="F20">
-        <f t="shared" ref="F20:H20" si="8">F19-F18</f>
-        <v>0.62000000000000011</v>
+        <v>6.77</v>
       </c>
       <c r="G20">
-        <f t="shared" si="8"/>
-        <v>0.55999999999999994</v>
+        <v>0.02</v>
       </c>
       <c r="H20">
-        <f t="shared" si="8"/>
-        <v>0.77999999999999403</v>
-      </c>
-      <c r="N20">
-        <f>AVERAGE(E20:H20)</f>
-        <v>0.66999999999999826</v>
-      </c>
-      <c r="AA20" t="s">
-        <v>122</v>
-      </c>
-      <c r="AB20" s="26">
-        <f t="shared" ref="AB20:AJ20" si="9">E4</f>
-        <v>10.72</v>
-      </c>
-      <c r="AC20" s="26">
-        <f t="shared" si="9"/>
-        <v>8.5399999999999991</v>
-      </c>
-      <c r="AD20" s="26">
-        <f t="shared" si="9"/>
-        <v>-3.12</v>
-      </c>
-      <c r="AE20" s="26">
-        <f t="shared" si="9"/>
-        <v>31.17</v>
-      </c>
-      <c r="AF20" s="26">
-        <f t="shared" si="9"/>
-        <v>8.5299999999999994</v>
-      </c>
-      <c r="AG20" s="26">
-        <f t="shared" si="9"/>
-        <v>31.99</v>
-      </c>
-      <c r="AH20" s="26">
-        <f t="shared" si="9"/>
-        <v>-13.59</v>
-      </c>
-      <c r="AI20" s="26">
-        <f t="shared" si="9"/>
-        <v>20.86</v>
-      </c>
-      <c r="AJ20" s="26">
-        <f t="shared" si="9"/>
-        <v>27.4</v>
+        <v>33.590000000000003</v>
       </c>
     </row>
     <row r="21" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B21" s="21" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="E21">
-        <f>E17-E18</f>
-        <v>0.27999999999999936</v>
+        <v>15.19</v>
       </c>
       <c r="F21">
-        <f t="shared" ref="F21:H21" si="10">F17-F18</f>
-        <v>0.30000000000000071</v>
+        <v>7.39</v>
       </c>
       <c r="G21">
-        <f t="shared" si="10"/>
-        <v>0.32999999999999996</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="H21">
-        <f t="shared" si="10"/>
-        <v>0.45999999999999375</v>
-      </c>
-      <c r="P21" s="26">
-        <f>AVERAGE(E21:H21)</f>
-        <v>0.34249999999999847</v>
+        <v>34.369999999999997</v>
       </c>
       <c r="AA21" t="s">
-        <v>126</v>
-      </c>
-      <c r="AB21" s="26">
-        <f t="shared" ref="AB21:AJ21" si="11">AB16-AB17</f>
-        <v>0.13999999999999993</v>
-      </c>
-      <c r="AC21" s="26">
-        <f t="shared" si="11"/>
-        <v>0.18999999999999886</v>
-      </c>
-      <c r="AD21" s="26">
-        <f t="shared" si="11"/>
-        <v>5.999999999999972E-2</v>
-      </c>
-      <c r="AE21" s="26">
-        <f t="shared" si="11"/>
-        <v>9.0000000000001995E-2</v>
-      </c>
-      <c r="AF21" s="26">
-        <f t="shared" si="11"/>
-        <v>0.15999999999999873</v>
-      </c>
-      <c r="AG21" s="26">
-        <f t="shared" si="11"/>
-        <v>0.1</v>
-      </c>
-      <c r="AH21" s="26">
-        <f t="shared" si="11"/>
-        <v>-2.9999999999999E-2</v>
-      </c>
-      <c r="AI21" s="26">
-        <f t="shared" si="11"/>
-        <v>0.19999999999999787</v>
-      </c>
-      <c r="AJ21" s="26">
-        <f t="shared" si="11"/>
-        <v>0.27999999999999969</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="AB21" s="37">
+        <f>World!C15</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AC21" s="37">
+        <f>World!D15</f>
+        <v>0.01</v>
+      </c>
+      <c r="AD21" s="37">
+        <f>World!E15</f>
+        <v>0.09</v>
+      </c>
+      <c r="AE21" s="37">
+        <f>World!F15</f>
+        <v>0.26</v>
+      </c>
+      <c r="AF21" s="37">
+        <f>World!G15</f>
+        <v>0.19</v>
+      </c>
+      <c r="AG21" s="37">
+        <f>World!H15</f>
+        <v>0.08</v>
+      </c>
+      <c r="AH21" s="37">
+        <f>World!I15</f>
+        <v>0.02</v>
+      </c>
+      <c r="AI21" s="37">
+        <f>World!J15</f>
+        <v>0.01</v>
+      </c>
+      <c r="AJ21" s="37"/>
     </row>
     <row r="22" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B22" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="E22">
+        <f>E21-E20</f>
+        <v>0.71999999999999886</v>
+      </c>
+      <c r="F22">
+        <f t="shared" ref="F22:H22" si="7">F21-F20</f>
+        <v>0.62000000000000011</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="7"/>
+        <v>0.55999999999999994</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="7"/>
+        <v>0.77999999999999403</v>
+      </c>
+      <c r="N22">
+        <f>AVERAGE(E22:H22)</f>
+        <v>0.66999999999999826</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>110</v>
+      </c>
+      <c r="AB22" s="26">
+        <f t="shared" ref="AB22:AJ22" si="8">E4</f>
+        <v>10.72</v>
+      </c>
+      <c r="AC22" s="26">
+        <f t="shared" si="8"/>
+        <v>8.5399999999999991</v>
+      </c>
+      <c r="AD22" s="26">
+        <f t="shared" si="8"/>
+        <v>-3.12</v>
+      </c>
+      <c r="AE22" s="26">
+        <f t="shared" si="8"/>
+        <v>31.17</v>
+      </c>
+      <c r="AF22" s="26">
+        <f t="shared" si="8"/>
+        <v>8.5299999999999994</v>
+      </c>
+      <c r="AG22" s="26">
+        <f t="shared" si="8"/>
+        <v>31.99</v>
+      </c>
+      <c r="AH22" s="26">
+        <f t="shared" si="8"/>
+        <v>-13.59</v>
+      </c>
+      <c r="AI22" s="26">
+        <f t="shared" si="8"/>
+        <v>20.86</v>
+      </c>
+      <c r="AJ22" s="26">
+        <f t="shared" si="8"/>
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="23" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B23" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="E23">
+        <f>E19-E20</f>
+        <v>0.27999999999999936</v>
+      </c>
+      <c r="F23">
+        <f t="shared" ref="F23:H23" si="9">F19-F20</f>
+        <v>0.30000000000000071</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="9"/>
+        <v>0.32999999999999996</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="9"/>
+        <v>0.45999999999999375</v>
+      </c>
+      <c r="P23" s="26">
+        <f>AVERAGE(E23:H23)</f>
+        <v>0.34249999999999847</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>114</v>
+      </c>
+      <c r="AB23" s="26">
+        <f t="shared" ref="AB23:AJ23" si="10">AB18-AB19</f>
+        <v>0.13999999999999993</v>
+      </c>
+      <c r="AC23" s="26">
+        <f t="shared" si="10"/>
+        <v>0.18999999999999886</v>
+      </c>
+      <c r="AD23" s="26">
+        <f t="shared" si="10"/>
+        <v>5.999999999999972E-2</v>
+      </c>
+      <c r="AE23" s="26">
+        <f t="shared" si="10"/>
+        <v>9.0000000000001995E-2</v>
+      </c>
+      <c r="AF23" s="26">
+        <f t="shared" si="10"/>
+        <v>0.15999999999999873</v>
+      </c>
+      <c r="AG23" s="26">
+        <f t="shared" si="10"/>
+        <v>0.1</v>
+      </c>
+      <c r="AH23" s="26">
+        <f t="shared" si="10"/>
+        <v>-2.9999999999999E-2</v>
+      </c>
+      <c r="AI23" s="26">
+        <f t="shared" si="10"/>
+        <v>0.19999999999999787</v>
+      </c>
+      <c r="AJ23" s="26">
+        <f t="shared" si="10"/>
+        <v>0.27999999999999969</v>
+      </c>
+    </row>
+    <row r="24" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B24" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="E22">
-        <f>E19-E17</f>
+      <c r="E24">
+        <f>E21-E19</f>
         <v>0.4399999999999995</v>
       </c>
-      <c r="F22">
-        <f t="shared" ref="F22:H22" si="12">F19-F17</f>
+      <c r="F24">
+        <f t="shared" ref="F24:H24" si="11">F21-F19</f>
         <v>0.3199999999999994</v>
       </c>
-      <c r="G22">
-        <f t="shared" si="12"/>
+      <c r="G24">
+        <f t="shared" si="11"/>
         <v>0.22999999999999998</v>
       </c>
-      <c r="H22">
-        <f t="shared" si="12"/>
+      <c r="H24">
+        <f t="shared" si="11"/>
         <v>0.32000000000000028</v>
       </c>
-      <c r="O22" s="28">
-        <f>AVERAGE(E22:H22)</f>
+      <c r="O24" s="28">
+        <f>AVERAGE(E24:H24)</f>
         <v>0.32749999999999979</v>
-      </c>
-    </row>
-    <row r="25" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B25" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="E25">
-        <v>1.81</v>
-      </c>
-      <c r="F25">
-        <v>10.79</v>
-      </c>
-      <c r="G25">
-        <v>-10.47</v>
-      </c>
-      <c r="H25">
-        <v>26.76</v>
-      </c>
-    </row>
-    <row r="26" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B26" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="E26">
-        <v>1.24</v>
-      </c>
-      <c r="F26">
-        <v>10.3</v>
-      </c>
-      <c r="G26">
-        <v>-10.89</v>
-      </c>
-      <c r="H26">
-        <v>26.14</v>
       </c>
     </row>
     <row r="27" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B27" s="21" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E27">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="F27">
-        <v>10.96</v>
+        <v>10.79</v>
       </c>
       <c r="G27">
-        <v>-10.3</v>
+        <v>-10.47</v>
       </c>
       <c r="H27">
-        <v>26.99</v>
+        <v>26.76</v>
       </c>
     </row>
     <row r="28" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B28" s="21" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="E28">
-        <f>E27-E26</f>
-        <v>0.65999999999999992</v>
+        <v>1.24</v>
       </c>
       <c r="F28">
-        <f t="shared" ref="F28:H28" si="13">F27-F26</f>
-        <v>0.66000000000000014</v>
+        <v>10.3</v>
       </c>
       <c r="G28">
-        <f t="shared" si="13"/>
-        <v>0.58999999999999986</v>
+        <v>-10.89</v>
       </c>
       <c r="H28">
-        <f t="shared" si="13"/>
-        <v>0.84999999999999787</v>
-      </c>
-      <c r="N28">
-        <f>AVERAGE(E28:H28)</f>
-        <v>0.6899999999999995</v>
+        <v>26.14</v>
       </c>
     </row>
     <row r="29" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B29" s="21" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="E29">
-        <f>E25-E26</f>
-        <v>0.57000000000000006</v>
+        <v>1.9</v>
       </c>
       <c r="F29">
-        <f t="shared" ref="F29:H29" si="14">F25-F26</f>
-        <v>0.48999999999999844</v>
+        <v>10.96</v>
       </c>
       <c r="G29">
-        <f t="shared" si="14"/>
-        <v>0.41999999999999993</v>
+        <v>-10.3</v>
       </c>
       <c r="H29">
-        <f t="shared" si="14"/>
-        <v>0.62000000000000099</v>
-      </c>
-      <c r="P29" s="26">
-        <f>AVERAGE(E29:H29)</f>
-        <v>0.52499999999999991</v>
+        <v>26.99</v>
       </c>
     </row>
     <row r="30" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B30" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="E30">
+        <f>E29-E28</f>
+        <v>0.65999999999999992</v>
+      </c>
+      <c r="F30">
+        <f t="shared" ref="F30:H30" si="12">F29-F28</f>
+        <v>0.66000000000000014</v>
+      </c>
+      <c r="G30">
+        <f t="shared" si="12"/>
+        <v>0.58999999999999986</v>
+      </c>
+      <c r="H30">
+        <f t="shared" si="12"/>
+        <v>0.84999999999999787</v>
+      </c>
+      <c r="N30">
+        <f>AVERAGE(E30:H30)</f>
+        <v>0.6899999999999995</v>
+      </c>
+    </row>
+    <row r="31" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B31" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="E31">
+        <f>E27-E28</f>
+        <v>0.57000000000000006</v>
+      </c>
+      <c r="F31">
+        <f t="shared" ref="F31:H31" si="13">F27-F28</f>
+        <v>0.48999999999999844</v>
+      </c>
+      <c r="G31">
+        <f t="shared" si="13"/>
+        <v>0.41999999999999993</v>
+      </c>
+      <c r="H31">
+        <f t="shared" si="13"/>
+        <v>0.62000000000000099</v>
+      </c>
+      <c r="P31" s="26">
+        <f>AVERAGE(E31:H31)</f>
+        <v>0.52499999999999991</v>
+      </c>
+    </row>
+    <row r="32" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B32" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="E30">
-        <f>E27-E25</f>
+      <c r="E32">
+        <f>E29-E27</f>
         <v>8.9999999999999858E-2</v>
       </c>
-      <c r="F30">
-        <f t="shared" ref="F30:H30" si="15">F27-F25</f>
+      <c r="F32">
+        <f t="shared" ref="F32:H32" si="14">F29-F27</f>
         <v>0.17000000000000171</v>
       </c>
-      <c r="G30">
-        <f t="shared" si="15"/>
+      <c r="G32">
+        <f t="shared" si="14"/>
         <v>0.16999999999999993</v>
       </c>
-      <c r="H30">
-        <f t="shared" si="15"/>
+      <c r="H32">
+        <f t="shared" si="14"/>
         <v>0.22999999999999687</v>
       </c>
-      <c r="O30" s="28">
-        <f>AVERAGE(E30:H30)</f>
+      <c r="O32" s="28">
+        <f>AVERAGE(E32:H32)</f>
         <v>0.16499999999999959</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B33" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="I33">
+    <row r="35" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B35" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="I35">
         <v>8.14</v>
       </c>
-      <c r="J33">
+      <c r="J35">
         <v>23.91</v>
       </c>
-      <c r="K33">
+      <c r="K35">
         <v>-15.2</v>
       </c>
-      <c r="L33">
+      <c r="L35">
         <v>12.01</v>
       </c>
-      <c r="M33">
+      <c r="M35">
         <v>14.23</v>
-      </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B34" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="I34">
-        <v>8.43</v>
-      </c>
-      <c r="J34">
-        <v>24.35</v>
-      </c>
-    </row>
-    <row r="35" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="I35">
-        <v>7.98</v>
-      </c>
-      <c r="J35">
-        <v>23.9</v>
-      </c>
-      <c r="K35">
-        <v>-15.41</v>
-      </c>
-      <c r="L35">
-        <v>11.86</v>
-      </c>
-      <c r="M35">
-        <v>14.11</v>
       </c>
     </row>
     <row r="36" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B36" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="I36">
+        <v>8.43</v>
+      </c>
+      <c r="J36">
+        <v>24.35</v>
+      </c>
+      <c r="K36">
+        <v>-15.03</v>
+      </c>
+      <c r="L36">
+        <v>12.39</v>
+      </c>
+      <c r="M36">
+        <v>14.62</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="I37">
+        <v>7.98</v>
+      </c>
+      <c r="J37">
+        <v>23.9</v>
+      </c>
+      <c r="K37">
+        <v>-15.41</v>
+      </c>
+      <c r="L37">
+        <v>11.86</v>
+      </c>
+      <c r="M37">
+        <v>14.11</v>
+      </c>
+    </row>
+    <row r="38" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B38" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="I36">
-        <f>I33-I35</f>
+      <c r="I38">
+        <f>I35-I37</f>
         <v>0.16000000000000014</v>
       </c>
-      <c r="J36">
-        <f>J33-J35</f>
+      <c r="J38">
+        <f>J35-J37</f>
         <v>1.0000000000001563E-2</v>
       </c>
-      <c r="K36">
-        <f t="shared" ref="K36:M36" si="16">K33-K35</f>
+      <c r="K38">
+        <f t="shared" ref="K38:M38" si="15">K35-K37</f>
         <v>0.21000000000000085</v>
       </c>
-      <c r="L36">
+      <c r="L38">
+        <f t="shared" si="15"/>
+        <v>0.15000000000000036</v>
+      </c>
+      <c r="M38">
+        <f t="shared" si="15"/>
+        <v>0.12000000000000099</v>
+      </c>
+      <c r="P38" s="26">
+        <f>AVERAGE(I38:M38)</f>
+        <v>0.13000000000000078</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B39" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="I39">
+        <f>I36-I35</f>
+        <v>0.28999999999999915</v>
+      </c>
+      <c r="J39">
+        <f>J36-J35</f>
+        <v>0.44000000000000128</v>
+      </c>
+      <c r="K39">
+        <f t="shared" ref="K39:M39" si="16">K36-K35</f>
+        <v>0.16999999999999993</v>
+      </c>
+      <c r="L39">
         <f t="shared" si="16"/>
-        <v>0.15000000000000036</v>
-      </c>
-      <c r="M36">
+        <v>0.38000000000000078</v>
+      </c>
+      <c r="M39">
         <f t="shared" si="16"/>
-        <v>0.12000000000000099</v>
-      </c>
-      <c r="P36" s="26">
-        <f>AVERAGE(I36:M36)</f>
-        <v>0.13000000000000078</v>
-      </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B37" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="I37">
-        <f>I34-I33</f>
-        <v>0.28999999999999915</v>
-      </c>
-      <c r="J37">
-        <f>J34-J33</f>
-        <v>0.44000000000000128</v>
-      </c>
-      <c r="O37" s="29">
-        <f>AVERAGE(I37:M37)</f>
-        <v>0.36500000000000021</v>
-      </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B43" s="1"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6"/>
-      <c r="G43" s="6"/>
+        <v>0.38999999999999879</v>
+      </c>
+      <c r="O39" s="29">
+        <f>AVERAGE(I39:M39)</f>
+        <v>0.33399999999999996</v>
+      </c>
     </row>
     <row r="44" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B44" s="1"/>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6"/>
-    </row>
-    <row r="49" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B49" s="1"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="6"/>
-      <c r="G49" s="6"/>
-    </row>
-    <row r="50" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B50" s="1"/>
-      <c r="C50" s="6"/>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6"/>
-      <c r="G50" s="6"/>
-    </row>
-    <row r="55" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B55" s="1"/>
-      <c r="C55" s="1"/>
-      <c r="D55" s="1"/>
-      <c r="E55" s="1"/>
-      <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
-    </row>
-    <row r="56" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B56" s="1"/>
-      <c r="C56" s="6"/>
-      <c r="D56" s="6"/>
-      <c r="E56" s="6"/>
-      <c r="F56" s="6"/>
-      <c r="G56" s="6"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B45" s="1"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="6"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B46" s="1"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+    </row>
+    <row r="51" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B51" s="1"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="6"/>
+    </row>
+    <row r="52" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B52" s="1"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="6"/>
     </row>
     <row r="57" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B57" s="1"/>
-      <c r="C57" s="6"/>
-      <c r="D57" s="6"/>
-      <c r="E57" s="6"/>
-      <c r="F57" s="6"/>
-    </row>
-    <row r="60" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="C60" s="1"/>
-      <c r="D60" s="1"/>
-      <c r="E60" s="1"/>
-      <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
-      <c r="I60" s="1"/>
-      <c r="J60" s="1"/>
-      <c r="K60" s="1"/>
-      <c r="L60" s="1"/>
-      <c r="M60" s="1"/>
-      <c r="N60" s="1"/>
-      <c r="O60" s="1"/>
-      <c r="P60" s="1"/>
-      <c r="Q60" s="1"/>
-    </row>
-    <row r="61" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B61" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+    </row>
+    <row r="58" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B58" s="1"/>
+      <c r="C58" s="6"/>
+      <c r="D58" s="6"/>
+      <c r="E58" s="6"/>
+      <c r="F58" s="6"/>
+      <c r="G58" s="6"/>
+    </row>
+    <row r="59" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B59" s="1"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="6"/>
+      <c r="F59" s="6"/>
     </row>
     <row r="62" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B62" s="1"/>
-      <c r="Q62" s="26"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
+      <c r="K62" s="1"/>
+      <c r="L62" s="1"/>
+      <c r="M62" s="1"/>
+      <c r="N62" s="1"/>
+      <c r="O62" s="1"/>
+      <c r="P62" s="1"/>
+      <c r="Q62" s="1"/>
     </row>
     <row r="63" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B63" s="1"/>
     </row>
+    <row r="64" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B64" s="1"/>
+      <c r="Q64" s="26"/>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B65" s="1"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="AB19:AJ19">
+  <conditionalFormatting sqref="AB21:AJ21">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB22:AJ22">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB23:AJ23">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E7:M7">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -5985,8 +6254,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB20:AJ20">
-    <cfRule type="colorScale" priority="4">
+  <conditionalFormatting sqref="E16:M16">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5997,7 +6266,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB21:AJ21">
+  <conditionalFormatting sqref="I39:M39">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>

--- a/NorthernTrust/NT-KostenBepaling.xlsx
+++ b/NorthernTrust/NT-KostenBepaling.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7c741cee80ec8cf3/Financieel/IndexFondsenOnderzoek/KeuzeWelkIndexFonds/OnderzoekPerFonds/NorthernTrust/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1756" documentId="13_ncr:1_{0BEEB54A-A1B5-4808-9253-8C962E6DCC11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E270FC32-E042-4A27-BA58-6741BA5EE756}"/>
+  <xr:revisionPtr revIDLastSave="1760" documentId="13_ncr:1_{0BEEB54A-A1B5-4808-9253-8C962E6DCC11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8952F43-EA37-44C7-A43C-A32EABE74EF7}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aannames" sheetId="4" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="Northern Trust Master fondsen" sheetId="2" r:id="rId7"/>
     <sheet name="Tracking Difference" sheetId="3" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -502,7 +502,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Gerben</t>
         </r>
@@ -511,7 +511,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 From "Sub-Fund Review" or "The returns posted by the Sub-Funds and their respective benchmarks for the year were as follows"
@@ -1048,7 +1048,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="9">
+  <numFmts count="10">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -1058,8 +1058,9 @@
     <numFmt numFmtId="169" formatCode="0.0%"/>
     <numFmt numFmtId="170" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="171" formatCode="_ * #,##0.0_ ;_ * \-#,##0.0_ ;_ * &quot;-&quot;?_ ;_ @_ "/>
+    <numFmt numFmtId="172" formatCode="0.000"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1131,19 +1132,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1181,7 +1169,7 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1227,6 +1215,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma" xfId="3" builtinId="3"/>
@@ -1246,10 +1235,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7101,6 +7086,7 @@
       <c r="N31" s="22"/>
       <c r="O31" s="22"/>
       <c r="P31" s="22"/>
+      <c r="Q31" s="39"/>
     </row>
     <row r="32" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B32" s="21" t="s">
@@ -7335,6 +7321,7 @@
       <c r="N37" s="22"/>
       <c r="O37" s="22"/>
       <c r="P37" s="22"/>
+      <c r="Q37" s="39"/>
     </row>
     <row r="38" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B38" s="21"/>
